--- a/tests/testthat/vlm_test_spec.xlsx
+++ b/tests/testthat/vlm_test_spec.xlsx
@@ -18,7 +18,7 @@
     <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Datasets!$A$1:$I$5</definedName>
     <definedName hidden="1" localSheetId="2" name="_xlnm._FilterDatabase">Variables!$A$1:$S$107</definedName>
     <definedName hidden="1" localSheetId="3" name="_xlnm._FilterDatabase">ValueLevel!$A$1:$R$17</definedName>
-    <definedName hidden="1" localSheetId="4" name="_xlnm._FilterDatabase">Codelists!$A$1:$H$295</definedName>
+    <definedName hidden="1" localSheetId="4" name="_xlnm._FilterDatabase">Codelists!$A$1:$H$205</definedName>
     <definedName hidden="1" localSheetId="5" name="_xlnm._FilterDatabase">Dictionaries!$A$1:$E$4</definedName>
     <definedName hidden="1" localSheetId="6" name="_xlnm._FilterDatabase">Methods!$A$1:$H$47</definedName>
     <definedName hidden="1" localSheetId="7" name="_xlnm._FilterDatabase">Comments!$A$1:$D$6</definedName>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3157" uniqueCount="762">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2655" uniqueCount="668">
   <si>
     <t>Attribute</t>
   </si>
@@ -1411,289 +1411,13 @@
     <t>Week 6</t>
   </si>
   <si>
-    <t>Week 7</t>
-  </si>
-  <si>
-    <t>Week 8</t>
-  </si>
-  <si>
-    <t>Week 9</t>
-  </si>
-  <si>
-    <t>Week 10</t>
-  </si>
-  <si>
-    <t>Week 11</t>
-  </si>
-  <si>
-    <t>Week 12</t>
-  </si>
-  <si>
-    <t>Week 13</t>
-  </si>
-  <si>
-    <t>Week 14</t>
-  </si>
-  <si>
-    <t>Week 15</t>
-  </si>
-  <si>
-    <t>Week 16</t>
-  </si>
-  <si>
-    <t>Week 17</t>
-  </si>
-  <si>
-    <t>Week 18</t>
-  </si>
-  <si>
-    <t>Week 19</t>
-  </si>
-  <si>
-    <t>Week 20</t>
-  </si>
-  <si>
-    <t>Week 21</t>
-  </si>
-  <si>
-    <t>Week 22</t>
-  </si>
-  <si>
-    <t>Week 23</t>
-  </si>
-  <si>
-    <t>Week 24</t>
-  </si>
-  <si>
-    <t>Week 25</t>
-  </si>
-  <si>
-    <t>Week 26</t>
-  </si>
-  <si>
-    <t>Week 27</t>
-  </si>
-  <si>
-    <t>Week 28</t>
-  </si>
-  <si>
-    <t>Week 29</t>
-  </si>
-  <si>
-    <t>Week 30</t>
-  </si>
-  <si>
-    <t>Week 31</t>
-  </si>
-  <si>
-    <t>Week 32</t>
-  </si>
-  <si>
-    <t>Week 33</t>
-  </si>
-  <si>
-    <t>Week 34</t>
-  </si>
-  <si>
-    <t>Week 35</t>
-  </si>
-  <si>
-    <t>Week 36</t>
-  </si>
-  <si>
-    <t>Week 37</t>
-  </si>
-  <si>
-    <t>Week 38</t>
-  </si>
-  <si>
-    <t>Week 39</t>
-  </si>
-  <si>
-    <t>Week 40</t>
-  </si>
-  <si>
-    <t>Week 41</t>
-  </si>
-  <si>
-    <t>Week 42</t>
-  </si>
-  <si>
-    <t>Week 43</t>
-  </si>
-  <si>
-    <t>Week 44</t>
-  </si>
-  <si>
-    <t>Week 45</t>
-  </si>
-  <si>
-    <t>Week 46</t>
-  </si>
-  <si>
-    <t>Week 47</t>
-  </si>
-  <si>
-    <t>Week 48</t>
-  </si>
-  <si>
-    <t>Week 49</t>
-  </si>
-  <si>
-    <t>Week 50</t>
-  </si>
-  <si>
-    <t>Week 51</t>
-  </si>
-  <si>
     <t>Codelist for ADEX.AVISITN</t>
   </si>
   <si>
-    <t>30.01</t>
-  </si>
-  <si>
-    <t>30.02</t>
-  </si>
-  <si>
-    <t>40.01</t>
-  </si>
-  <si>
-    <t>40.02</t>
-  </si>
-  <si>
-    <t>40.03</t>
-  </si>
-  <si>
-    <t>40.04</t>
-  </si>
-  <si>
-    <t>40.05</t>
-  </si>
-  <si>
-    <t>40.06</t>
-  </si>
-  <si>
-    <t>40.07</t>
-  </si>
-  <si>
-    <t>50.01</t>
-  </si>
-  <si>
-    <t>50.02</t>
-  </si>
-  <si>
-    <t>50.03</t>
-  </si>
-  <si>
-    <t>50.04</t>
-  </si>
-  <si>
-    <t>50.05</t>
-  </si>
-  <si>
-    <t>50.06</t>
-  </si>
-  <si>
-    <t>50.07</t>
-  </si>
-  <si>
-    <t>50.08</t>
-  </si>
-  <si>
-    <t>50.09</t>
-  </si>
-  <si>
-    <t>50.1</t>
-  </si>
-  <si>
-    <t>50.11</t>
-  </si>
-  <si>
-    <t>50.12</t>
-  </si>
-  <si>
-    <t>50.13</t>
-  </si>
-  <si>
-    <t>60.01</t>
-  </si>
-  <si>
-    <t>60.02</t>
-  </si>
-  <si>
-    <t>60.03</t>
-  </si>
-  <si>
-    <t>60.04</t>
-  </si>
-  <si>
-    <t>60.05</t>
-  </si>
-  <si>
-    <t>60.06</t>
-  </si>
-  <si>
-    <t>60.07</t>
-  </si>
-  <si>
-    <t>60.08</t>
-  </si>
-  <si>
-    <t>60.09</t>
-  </si>
-  <si>
-    <t>60.1</t>
-  </si>
-  <si>
-    <t>60.11</t>
-  </si>
-  <si>
-    <t>60.12</t>
-  </si>
-  <si>
-    <t>60.13</t>
-  </si>
-  <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>70.01</t>
-  </si>
-  <si>
-    <t>70.02</t>
-  </si>
-  <si>
-    <t>70.03</t>
-  </si>
-  <si>
-    <t>70.04</t>
-  </si>
-  <si>
-    <t>70.05</t>
-  </si>
-  <si>
-    <t>70.06</t>
-  </si>
-  <si>
-    <t>70.07</t>
-  </si>
-  <si>
-    <t>70.08</t>
-  </si>
-  <si>
-    <t>70.09</t>
-  </si>
-  <si>
-    <t>70.1</t>
-  </si>
-  <si>
-    <t>70.11</t>
-  </si>
-  <si>
     <t>Codelist for ADEX.EXDOSFRM</t>
   </si>
   <si>
-    <t>SYRINGE SAFETY DEVICE</t>
+    <t>SYRINGE</t>
   </si>
   <si>
     <t>Codelist for ADEX.EXDOSFRQ</t>
@@ -1717,10 +1441,10 @@
     <t>Codelist for ADEX.EXTRT</t>
   </si>
   <si>
-    <t>Draft-Belimumab</t>
-  </si>
-  <si>
-    <t>Draft-Placebo</t>
+    <t>Placebo</t>
+  </si>
+  <si>
+    <t>Active Treatment</t>
   </si>
   <si>
     <t>Codelist for ADEX.PARAM</t>
@@ -1952,12 +1676,6 @@
   </si>
   <si>
     <t>Treatment Assignments</t>
-  </si>
-  <si>
-    <t>Placebo</t>
-  </si>
-  <si>
-    <t>Active Treatment</t>
   </si>
   <si>
     <t>888</t>
@@ -11640,4831 +11358,3256 @@
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>53</v>
+        <v>179</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>460</v>
+        <v>50</v>
+      </c>
+      <c r="F43" s="5">
+        <v>10.0</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>53</v>
+        <v>179</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>461</v>
+        <v>56</v>
+      </c>
+      <c r="F44" s="5">
+        <v>20.0</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="45" ht="14.25" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>53</v>
+        <v>179</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>462</v>
+        <v>61</v>
+      </c>
+      <c r="F45" s="5">
+        <v>30.0</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>53</v>
+        <v>179</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>463</v>
+        <v>65</v>
+      </c>
+      <c r="F46" s="5">
+        <v>40.0</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>53</v>
+        <v>179</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>464</v>
+        <v>69</v>
+      </c>
+      <c r="F47" s="5">
+        <v>50.0</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>53</v>
+        <v>179</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>465</v>
+        <v>54</v>
+      </c>
+      <c r="F48" s="5">
+        <v>60.0</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>53</v>
+        <v>179</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>466</v>
+        <v>79</v>
+      </c>
+      <c r="F49" s="5">
+        <v>70.0</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="50" ht="14.25" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>467</v>
+        <v>50</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>187</v>
+        <v>212</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>126</v>
+        <v>50</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="53" ht="14.25" customHeight="1">
       <c r="A53" s="2" t="s">
-        <v>187</v>
+        <v>217</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>452</v>
+        <v>469</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>471</v>
+        <v>50</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="55" ht="14.25" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>452</v>
+        <v>469</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>472</v>
+        <v>56</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="56" ht="14.25" customHeight="1">
       <c r="A56" s="2" t="s">
-        <v>187</v>
+        <v>252</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>452</v>
+        <v>472</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>145</v>
+        <v>50</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>473</v>
+        <v>387</v>
       </c>
     </row>
     <row r="57" ht="14.25" customHeight="1">
       <c r="A57" s="2" t="s">
-        <v>187</v>
+        <v>252</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>452</v>
+        <v>472</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>149</v>
+        <v>56</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>474</v>
+        <v>393</v>
       </c>
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>187</v>
+        <v>252</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>452</v>
+        <v>472</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>154</v>
+        <v>61</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="59" ht="14.25" customHeight="1">
       <c r="A59" s="2" t="s">
-        <v>187</v>
+        <v>252</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>452</v>
+        <v>472</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>159</v>
+        <v>65</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="60" ht="14.25" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>187</v>
+        <v>252</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>452</v>
+        <v>472</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>164</v>
+        <v>69</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>477</v>
+        <v>399</v>
       </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>187</v>
+        <v>257</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>452</v>
+        <v>475</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>168</v>
+        <v>50</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>478</v>
+        <v>196</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="62" ht="14.25" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>187</v>
+        <v>257</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>452</v>
+        <v>475</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>172</v>
+        <v>56</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c r="A63" s="2" t="s">
-        <v>187</v>
+        <v>257</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>452</v>
+        <v>475</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>176</v>
+        <v>61</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>480</v>
+        <v>477</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>187</v>
+        <v>257</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>452</v>
+        <v>475</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>183</v>
+        <v>65</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>481</v>
+        <v>478</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="65" ht="14.25" customHeight="1">
       <c r="A65" s="2" t="s">
-        <v>187</v>
+        <v>257</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>452</v>
+        <v>475</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>190</v>
+        <v>69</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>482</v>
+        <v>479</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c r="A66" s="2" t="s">
-        <v>187</v>
+        <v>262</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>452</v>
+        <v>480</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>195</v>
+        <v>50</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>483</v>
+        <v>50</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c r="A67" s="2" t="s">
-        <v>187</v>
+        <v>262</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>452</v>
+        <v>480</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>199</v>
+        <v>56</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>484</v>
+        <v>56</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="68" ht="14.25" customHeight="1">
       <c r="A68" s="2" t="s">
-        <v>187</v>
+        <v>262</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>452</v>
+        <v>480</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>204</v>
+        <v>61</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>485</v>
+        <v>61</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="2" t="s">
-        <v>187</v>
+        <v>262</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>452</v>
+        <v>480</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>209</v>
+        <v>65</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>486</v>
+        <v>65</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="70" ht="14.25" customHeight="1">
       <c r="A70" s="2" t="s">
-        <v>187</v>
+        <v>262</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>452</v>
+        <v>480</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>214</v>
+        <v>69</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>487</v>
+        <v>69</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c r="A71" s="2" t="s">
-        <v>187</v>
+        <v>291</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>452</v>
+        <v>291</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>219</v>
+        <v>50</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1">
       <c r="A72" s="2" t="s">
-        <v>187</v>
+        <v>291</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>452</v>
+        <v>291</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>223</v>
+        <v>56</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c r="A73" s="2" t="s">
-        <v>187</v>
+        <v>291</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>452</v>
+        <v>291</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>227</v>
+        <v>61</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>187</v>
+        <v>295</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>452</v>
+        <v>295</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>231</v>
+        <v>50</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>491</v>
+        <v>50</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="75" ht="14.25" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>187</v>
+        <v>295</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>452</v>
+        <v>295</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>133</v>
+        <v>56</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>492</v>
+        <v>56</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="76" ht="14.25" customHeight="1">
       <c r="A76" s="2" t="s">
-        <v>187</v>
+        <v>295</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>452</v>
+        <v>295</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>493</v>
+        <v>61</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
       <c r="A77" s="2" t="s">
-        <v>187</v>
+        <v>298</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>452</v>
+        <v>298</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>241</v>
+        <v>50</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c r="A78" s="2" t="s">
-        <v>187</v>
+        <v>298</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>452</v>
+        <v>298</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>245</v>
+        <v>56</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
     </row>
     <row r="79" ht="14.25" customHeight="1">
       <c r="A79" s="2" t="s">
-        <v>187</v>
+        <v>302</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>452</v>
+        <v>302</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>249</v>
+        <v>50</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>496</v>
+        <v>50</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="80" ht="14.25" customHeight="1">
       <c r="A80" s="2" t="s">
-        <v>187</v>
+        <v>302</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>452</v>
+        <v>302</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>254</v>
+        <v>56</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>497</v>
+        <v>56</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>485</v>
       </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c r="A81" s="2" t="s">
-        <v>187</v>
+        <v>77</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>452</v>
+        <v>486</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>487</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>259</v>
+        <v>69</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>498</v>
+        <v>488</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
       <c r="A82" s="2" t="s">
-        <v>187</v>
+        <v>97</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>452</v>
+        <v>95</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>263</v>
+        <v>50</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c r="A83" s="2" t="s">
-        <v>187</v>
+        <v>97</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>452</v>
+        <v>95</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>266</v>
+        <v>56</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
     </row>
     <row r="84" ht="14.25" customHeight="1">
       <c r="A84" s="2" t="s">
-        <v>187</v>
+        <v>97</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>452</v>
+        <v>95</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>269</v>
+        <v>61</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
     </row>
     <row r="85" ht="14.25" customHeight="1">
       <c r="A85" s="2" t="s">
-        <v>187</v>
+        <v>97</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>452</v>
+        <v>95</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>272</v>
+        <v>65</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
       <c r="A86" s="2" t="s">
-        <v>187</v>
+        <v>97</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>452</v>
+        <v>95</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>364</v>
+        <v>69</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
       <c r="A87" s="2" t="s">
-        <v>187</v>
+        <v>97</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>452</v>
+        <v>95</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>368</v>
+        <v>54</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
     </row>
     <row r="88" ht="14.25" customHeight="1">
       <c r="A88" s="2" t="s">
-        <v>180</v>
+        <v>97</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>505</v>
+        <v>95</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>179</v>
+        <v>53</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="H88" s="2" t="s">
-        <v>453</v>
+        <v>497</v>
       </c>
     </row>
     <row r="89" ht="14.25" customHeight="1">
       <c r="A89" s="2" t="s">
-        <v>180</v>
+        <v>97</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>505</v>
+        <v>95</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>179</v>
+        <v>53</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="H89" s="2" t="s">
-        <v>454</v>
+        <v>498</v>
       </c>
     </row>
     <row r="90" ht="14.25" customHeight="1">
       <c r="A90" s="2" t="s">
-        <v>180</v>
+        <v>97</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>505</v>
+        <v>95</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>179</v>
+        <v>53</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>455</v>
+        <v>499</v>
       </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
       <c r="A91" s="2" t="s">
-        <v>180</v>
+        <v>97</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>505</v>
+        <v>95</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>179</v>
+        <v>53</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="H91" s="2" t="s">
-        <v>456</v>
+        <v>500</v>
       </c>
     </row>
     <row r="92" ht="14.25" customHeight="1">
       <c r="A92" s="2" t="s">
-        <v>180</v>
+        <v>97</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>505</v>
+        <v>95</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>179</v>
+        <v>53</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H92" s="2" t="s">
-        <v>457</v>
+        <v>501</v>
       </c>
     </row>
     <row r="93" ht="14.25" customHeight="1">
       <c r="A93" s="2" t="s">
-        <v>180</v>
+        <v>97</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>505</v>
+        <v>95</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>179</v>
+        <v>53</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>54</v>
+        <v>104</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="H93" s="2" t="s">
-        <v>458</v>
+        <v>502</v>
       </c>
     </row>
     <row r="94" ht="14.25" customHeight="1">
       <c r="A94" s="2" t="s">
-        <v>180</v>
+        <v>97</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>505</v>
+        <v>95</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>179</v>
+        <v>53</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="H94" s="2" t="s">
-        <v>459</v>
+        <v>503</v>
       </c>
     </row>
     <row r="95" ht="14.25" customHeight="1">
       <c r="A95" s="2" t="s">
-        <v>180</v>
+        <v>97</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>505</v>
+        <v>95</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>179</v>
+        <v>53</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="H95" s="2" t="s">
-        <v>460</v>
+        <v>504</v>
       </c>
     </row>
     <row r="96" ht="14.25" customHeight="1">
       <c r="A96" s="2" t="s">
-        <v>180</v>
+        <v>97</v>
       </c>
       <c r="B96" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F96" s="2" t="s">
         <v>505</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="H96" s="2" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
       <c r="A97" s="2" t="s">
-        <v>180</v>
+        <v>97</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>505</v>
+        <v>95</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>179</v>
+        <v>53</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="H97" s="2" t="s">
-        <v>462</v>
+        <v>506</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
       <c r="A98" s="2" t="s">
-        <v>180</v>
+        <v>97</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>505</v>
+        <v>95</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>179</v>
+        <v>53</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>463</v>
+        <v>507</v>
       </c>
     </row>
     <row r="99" ht="14.25" customHeight="1">
       <c r="A99" s="2" t="s">
-        <v>180</v>
+        <v>102</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>505</v>
+        <v>101</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>104</v>
+        <v>50</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>514</v>
+        <v>50</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>464</v>
+        <v>491</v>
       </c>
     </row>
     <row r="100" ht="14.25" customHeight="1">
       <c r="A100" s="2" t="s">
-        <v>180</v>
+        <v>102</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>505</v>
+        <v>101</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>272</v>
+        <v>56</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>465</v>
+        <v>492</v>
       </c>
     </row>
     <row r="101" ht="14.25" customHeight="1">
       <c r="A101" s="2" t="s">
-        <v>180</v>
+        <v>102</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>505</v>
+        <v>101</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>114</v>
+        <v>61</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>515</v>
+        <v>61</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>466</v>
+        <v>493</v>
       </c>
     </row>
     <row r="102" ht="14.25" customHeight="1">
       <c r="A102" s="2" t="s">
-        <v>180</v>
+        <v>102</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>505</v>
+        <v>101</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>118</v>
+        <v>65</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>516</v>
+        <v>65</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>467</v>
+        <v>494</v>
       </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
       <c r="A103" s="2" t="s">
-        <v>180</v>
+        <v>102</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>505</v>
+        <v>101</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>122</v>
+        <v>69</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>517</v>
+        <v>69</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>468</v>
+        <v>495</v>
       </c>
     </row>
     <row r="104" ht="14.25" customHeight="1">
       <c r="A104" s="2" t="s">
-        <v>180</v>
+        <v>102</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>505</v>
+        <v>101</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>126</v>
+        <v>54</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>518</v>
+        <v>54</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>469</v>
+        <v>496</v>
       </c>
     </row>
     <row r="105" ht="14.25" customHeight="1">
       <c r="A105" s="2" t="s">
-        <v>180</v>
+        <v>102</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>505</v>
+        <v>101</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>519</v>
+        <v>79</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>470</v>
+        <v>497</v>
       </c>
     </row>
     <row r="106" ht="14.25" customHeight="1">
       <c r="A106" s="2" t="s">
-        <v>180</v>
+        <v>102</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>505</v>
+        <v>101</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>136</v>
+        <v>73</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>520</v>
+        <v>73</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>471</v>
+        <v>498</v>
       </c>
     </row>
     <row r="107" ht="14.25" customHeight="1">
       <c r="A107" s="2" t="s">
-        <v>180</v>
+        <v>102</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>505</v>
+        <v>101</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>141</v>
+        <v>89</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>521</v>
+        <v>89</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>472</v>
+        <v>499</v>
       </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
       <c r="A108" s="2" t="s">
-        <v>180</v>
+        <v>102</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>505</v>
+        <v>101</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>145</v>
+        <v>93</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>522</v>
+        <v>93</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>473</v>
+        <v>500</v>
       </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
       <c r="A109" s="2" t="s">
-        <v>180</v>
+        <v>102</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>505</v>
+        <v>101</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>149</v>
+        <v>99</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>523</v>
+        <v>99</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>474</v>
+        <v>501</v>
       </c>
     </row>
     <row r="110" ht="14.25" customHeight="1">
       <c r="A110" s="2" t="s">
-        <v>180</v>
+        <v>102</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>505</v>
+        <v>101</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>154</v>
+        <v>104</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>524</v>
+        <v>104</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>475</v>
+        <v>502</v>
       </c>
     </row>
     <row r="111" ht="14.25" customHeight="1">
       <c r="A111" s="2" t="s">
-        <v>180</v>
+        <v>102</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>505</v>
+        <v>101</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>159</v>
+        <v>59</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>525</v>
+        <v>59</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>476</v>
+        <v>503</v>
       </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
       <c r="A112" s="2" t="s">
-        <v>180</v>
+        <v>102</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>505</v>
+        <v>101</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>164</v>
+        <v>114</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>526</v>
+        <v>114</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>477</v>
+        <v>504</v>
       </c>
     </row>
     <row r="113" ht="14.25" customHeight="1">
       <c r="A113" s="2" t="s">
-        <v>180</v>
+        <v>102</v>
       </c>
       <c r="B113" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H113" s="2" t="s">
         <v>505</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="E113" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="F113" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="H113" s="2" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="114" ht="14.25" customHeight="1">
       <c r="A114" s="2" t="s">
-        <v>180</v>
+        <v>102</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>505</v>
+        <v>101</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>172</v>
+        <v>122</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>479</v>
+        <v>506</v>
       </c>
     </row>
     <row r="115" ht="14.25" customHeight="1">
       <c r="A115" s="2" t="s">
-        <v>180</v>
+        <v>102</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>505</v>
+        <v>101</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>176</v>
+        <v>126</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>528</v>
+        <v>126</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>480</v>
+        <v>507</v>
       </c>
     </row>
     <row r="116" ht="14.25" customHeight="1">
       <c r="A116" s="2" t="s">
-        <v>180</v>
+        <v>508</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>183</v>
+        <v>50</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>529</v>
+        <v>50</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>481</v>
+        <v>509</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
       <c r="A117" s="2" t="s">
-        <v>180</v>
+        <v>508</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>190</v>
+        <v>56</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>530</v>
+        <v>56</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>482</v>
+        <v>510</v>
       </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
       <c r="A118" s="2" t="s">
-        <v>180</v>
+        <v>508</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>195</v>
+        <v>61</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>531</v>
+        <v>61</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>483</v>
+        <v>511</v>
       </c>
     </row>
     <row r="119" ht="14.25" customHeight="1">
       <c r="A119" s="2" t="s">
-        <v>180</v>
+        <v>512</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>179</v>
+        <v>53</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>199</v>
+        <v>50</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="H119" s="2" t="s">
-        <v>484</v>
+        <v>509</v>
       </c>
     </row>
     <row r="120" ht="14.25" customHeight="1">
       <c r="A120" s="2" t="s">
-        <v>180</v>
+        <v>512</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>179</v>
+        <v>53</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>204</v>
+        <v>56</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="H120" s="2" t="s">
-        <v>485</v>
+        <v>510</v>
       </c>
     </row>
     <row r="121" ht="14.25" customHeight="1">
       <c r="A121" s="2" t="s">
-        <v>180</v>
+        <v>512</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>179</v>
+        <v>53</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>209</v>
+        <v>61</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="H121" s="2" t="s">
-        <v>486</v>
+        <v>511</v>
       </c>
     </row>
     <row r="122" ht="14.25" customHeight="1">
       <c r="A122" s="2" t="s">
-        <v>180</v>
+        <v>513</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>179</v>
+        <v>53</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>214</v>
+        <v>50</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="H122" s="2" t="s">
-        <v>487</v>
+        <v>514</v>
       </c>
     </row>
     <row r="123" ht="14.25" customHeight="1">
       <c r="A123" s="2" t="s">
-        <v>180</v>
+        <v>513</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>179</v>
+        <v>53</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>219</v>
+        <v>56</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="H123" s="2" t="s">
-        <v>488</v>
+        <v>515</v>
       </c>
     </row>
     <row r="124" ht="14.25" customHeight="1">
       <c r="A124" s="2" t="s">
-        <v>180</v>
+        <v>513</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>179</v>
+        <v>53</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>223</v>
+        <v>61</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="H124" s="2" t="s">
-        <v>489</v>
+        <v>516</v>
       </c>
     </row>
     <row r="125" ht="14.25" customHeight="1">
       <c r="A125" s="2" t="s">
-        <v>180</v>
+        <v>513</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>179</v>
+        <v>53</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>227</v>
+        <v>65</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="H125" s="2" t="s">
-        <v>490</v>
+        <v>517</v>
       </c>
     </row>
     <row r="126" ht="14.25" customHeight="1">
       <c r="A126" s="2" t="s">
-        <v>180</v>
+        <v>513</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>179</v>
+        <v>53</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>231</v>
+        <v>69</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="H126" s="2" t="s">
-        <v>491</v>
+        <v>518</v>
       </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
       <c r="A127" s="2" t="s">
-        <v>180</v>
+        <v>108</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>505</v>
+        <v>519</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>520</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>179</v>
+        <v>53</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>133</v>
+        <v>50</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="H127" s="2" t="s">
-        <v>492</v>
+        <v>521</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="128" ht="14.25" customHeight="1">
       <c r="A128" s="2" t="s">
-        <v>180</v>
+        <v>108</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>505</v>
+        <v>519</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>520</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>179</v>
+        <v>53</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="H128" s="2" t="s">
-        <v>493</v>
+        <v>523</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="129" ht="14.25" customHeight="1">
       <c r="A129" s="2" t="s">
-        <v>180</v>
+        <v>108</v>
       </c>
       <c r="B129" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F129" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="D129" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="E129" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="F129" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="H129" s="2" t="s">
-        <v>494</v>
+      <c r="G129" s="2" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="130" ht="14.25" customHeight="1">
       <c r="A130" s="2" t="s">
-        <v>180</v>
+        <v>108</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>505</v>
+        <v>519</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>520</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>179</v>
+        <v>53</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>245</v>
+        <v>65</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="H130" s="2" t="s">
-        <v>495</v>
+        <v>506</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="131" ht="14.25" customHeight="1">
       <c r="A131" s="2" t="s">
-        <v>180</v>
+        <v>527</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>505</v>
+        <v>527</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>249</v>
+        <v>50</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>544</v>
+        <v>50</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
     </row>
     <row r="132" ht="14.25" customHeight="1">
       <c r="A132" s="2" t="s">
-        <v>180</v>
+        <v>527</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>505</v>
+        <v>527</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>254</v>
+        <v>56</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>545</v>
+        <v>56</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>497</v>
+        <v>510</v>
       </c>
     </row>
     <row r="133" ht="14.25" customHeight="1">
       <c r="A133" s="2" t="s">
-        <v>180</v>
+        <v>527</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>505</v>
+        <v>527</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>259</v>
+        <v>61</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>546</v>
+        <v>61</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>498</v>
+        <v>511</v>
       </c>
     </row>
     <row r="134" ht="14.25" customHeight="1">
       <c r="A134" s="2" t="s">
-        <v>180</v>
+        <v>528</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>505</v>
+        <v>528</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>179</v>
+        <v>53</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>263</v>
+        <v>50</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="H134" s="2" t="s">
-        <v>499</v>
+        <v>509</v>
       </c>
     </row>
     <row r="135" ht="14.25" customHeight="1">
       <c r="A135" s="2" t="s">
-        <v>180</v>
+        <v>528</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>505</v>
+        <v>528</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>179</v>
+        <v>53</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>266</v>
+        <v>56</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="H135" s="2" t="s">
-        <v>500</v>
+        <v>510</v>
       </c>
     </row>
     <row r="136" ht="14.25" customHeight="1">
       <c r="A136" s="2" t="s">
-        <v>180</v>
+        <v>528</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>505</v>
+        <v>528</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>179</v>
+        <v>53</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>269</v>
+        <v>61</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="H136" s="2" t="s">
-        <v>501</v>
+        <v>511</v>
       </c>
     </row>
     <row r="137" ht="14.25" customHeight="1">
       <c r="A137" s="2" t="s">
-        <v>180</v>
+        <v>87</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>505</v>
+        <v>85</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>529</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>179</v>
+        <v>53</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>272</v>
+        <v>50</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="H137" s="2" t="s">
-        <v>502</v>
+        <v>491</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>530</v>
       </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
       <c r="A138" s="2" t="s">
-        <v>180</v>
+        <v>87</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>505</v>
+        <v>85</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>529</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>179</v>
+        <v>53</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>364</v>
+        <v>56</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="H138" s="2" t="s">
-        <v>503</v>
+        <v>531</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="139" ht="14.25" customHeight="1">
       <c r="A139" s="2" t="s">
-        <v>180</v>
+        <v>87</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>505</v>
+        <v>85</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>529</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>179</v>
+        <v>53</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>368</v>
+        <v>61</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="H139" s="2" t="s">
-        <v>504</v>
+        <v>497</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="140" ht="14.25" customHeight="1">
       <c r="A140" s="2" t="s">
-        <v>207</v>
+        <v>87</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>553</v>
+        <v>85</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>529</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>554</v>
+        <v>498</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="141" ht="14.25" customHeight="1">
       <c r="A141" s="2" t="s">
-        <v>212</v>
+        <v>87</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>555</v>
+        <v>85</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>529</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>556</v>
+        <v>499</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
       <c r="A142" s="2" t="s">
-        <v>202</v>
+        <v>87</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>557</v>
+        <v>85</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>529</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>558</v>
+        <v>536</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
       <c r="A143" s="2" t="s">
-        <v>217</v>
+        <v>87</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>559</v>
+        <v>85</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>529</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>560</v>
+        <v>505</v>
+      </c>
+      <c r="G143" s="2" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="144" ht="14.25" customHeight="1">
       <c r="A144" s="2" t="s">
-        <v>193</v>
+        <v>87</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>561</v>
+        <v>85</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>529</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>562</v>
+        <v>506</v>
+      </c>
+      <c r="G144" s="2" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="145" ht="14.25" customHeight="1">
       <c r="A145" s="2" t="s">
-        <v>193</v>
+        <v>305</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>561</v>
+        <v>91</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>563</v>
+        <v>50</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="146" ht="14.25" customHeight="1">
       <c r="A146" s="2" t="s">
-        <v>252</v>
+        <v>305</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>564</v>
+        <v>91</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>387</v>
+        <v>56</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
       <c r="A147" s="2" t="s">
-        <v>252</v>
+        <v>305</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>564</v>
+        <v>91</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>393</v>
+        <v>61</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="148" ht="14.25" customHeight="1">
       <c r="A148" s="2" t="s">
-        <v>252</v>
+        <v>305</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>564</v>
+        <v>91</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>565</v>
+        <v>65</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
       <c r="A149" s="2" t="s">
-        <v>252</v>
+        <v>305</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>564</v>
+        <v>91</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>566</v>
+        <v>69</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="150" ht="14.25" customHeight="1">
       <c r="A150" s="2" t="s">
-        <v>252</v>
+        <v>305</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>564</v>
+        <v>91</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>399</v>
+        <v>54</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>536</v>
       </c>
     </row>
     <row r="151" ht="14.25" customHeight="1">
       <c r="A151" s="2" t="s">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>567</v>
+        <v>91</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>196</v>
+        <v>79</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>387</v>
+        <v>505</v>
       </c>
     </row>
     <row r="152" ht="14.25" customHeight="1">
       <c r="A152" s="2" t="s">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>567</v>
+        <v>91</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>568</v>
+        <v>73</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>393</v>
+        <v>506</v>
       </c>
     </row>
     <row r="153" ht="14.25" customHeight="1">
       <c r="A153" s="2" t="s">
-        <v>257</v>
+        <v>308</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>567</v>
+        <v>307</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="H153" s="2" t="s">
-        <v>565</v>
+        <v>491</v>
       </c>
     </row>
     <row r="154" ht="14.25" customHeight="1">
       <c r="A154" s="2" t="s">
-        <v>257</v>
+        <v>308</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>567</v>
+        <v>307</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="H154" s="2" t="s">
-        <v>566</v>
+        <v>492</v>
       </c>
     </row>
     <row r="155" ht="14.25" customHeight="1">
       <c r="A155" s="2" t="s">
-        <v>257</v>
+        <v>308</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>567</v>
+        <v>307</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="H155" s="2" t="s">
-        <v>399</v>
+        <v>493</v>
       </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
       <c r="A156" s="2" t="s">
-        <v>262</v>
+        <v>308</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>572</v>
+        <v>307</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H156" s="2" t="s">
-        <v>387</v>
+        <v>494</v>
       </c>
     </row>
     <row r="157" ht="14.25" customHeight="1">
       <c r="A157" s="2" t="s">
-        <v>262</v>
+        <v>308</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>572</v>
+        <v>307</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H157" s="2" t="s">
-        <v>393</v>
+        <v>495</v>
       </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
       <c r="A158" s="2" t="s">
-        <v>262</v>
+        <v>308</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>572</v>
+        <v>307</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H158" s="2" t="s">
-        <v>565</v>
+        <v>496</v>
       </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
       <c r="A159" s="2" t="s">
-        <v>262</v>
+        <v>308</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>572</v>
+        <v>307</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H159" s="2" t="s">
-        <v>566</v>
+        <v>497</v>
       </c>
     </row>
     <row r="160" ht="14.25" customHeight="1">
       <c r="A160" s="2" t="s">
-        <v>262</v>
+        <v>308</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>572</v>
+        <v>307</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H160" s="2" t="s">
-        <v>399</v>
+        <v>498</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
       <c r="A161" s="2" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>573</v>
+        <v>500</v>
       </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
       <c r="A162" s="2" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>574</v>
+        <v>501</v>
       </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
       <c r="A163" s="2" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>575</v>
+        <v>536</v>
       </c>
     </row>
     <row r="164" ht="14.25" customHeight="1">
       <c r="A164" s="2" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H164" s="2" t="s">
-        <v>573</v>
+        <v>506</v>
       </c>
     </row>
     <row r="165" ht="14.25" customHeight="1">
       <c r="A165" s="2" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H165" s="2" t="s">
-        <v>574</v>
+        <v>507</v>
       </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
       <c r="A166" s="2" t="s">
-        <v>295</v>
+        <v>312</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>72</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>575</v>
+        <v>491</v>
       </c>
     </row>
     <row r="167" ht="14.25" customHeight="1">
       <c r="A167" s="2" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>576</v>
+        <v>56</v>
+      </c>
+      <c r="H167" s="2" t="s">
+        <v>492</v>
       </c>
     </row>
     <row r="168" ht="14.25" customHeight="1">
       <c r="A168" s="2" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>577</v>
+        <v>61</v>
+      </c>
+      <c r="H168" s="2" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="169" ht="14.25" customHeight="1">
       <c r="A169" s="2" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>72</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>576</v>
+        <v>494</v>
       </c>
     </row>
     <row r="170" ht="14.25" customHeight="1">
       <c r="A170" s="2" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>72</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>577</v>
+        <v>495</v>
       </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
       <c r="A171" s="2" t="s">
-        <v>77</v>
+        <v>312</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="C171" s="2" t="s">
-        <v>579</v>
+        <v>311</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="G171" s="2" t="s">
-        <v>581</v>
+        <v>54</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>582</v>
+        <v>496</v>
       </c>
     </row>
     <row r="172" ht="14.25" customHeight="1">
       <c r="A172" s="2" t="s">
-        <v>97</v>
+        <v>312</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>95</v>
+        <v>311</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>583</v>
+        <v>79</v>
+      </c>
+      <c r="H172" s="2" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="173" ht="14.25" customHeight="1">
       <c r="A173" s="2" t="s">
-        <v>97</v>
+        <v>312</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>95</v>
+        <v>311</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>584</v>
+        <v>73</v>
+      </c>
+      <c r="H173" s="2" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="174" ht="14.25" customHeight="1">
       <c r="A174" s="2" t="s">
-        <v>97</v>
+        <v>312</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>95</v>
+        <v>311</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>585</v>
+        <v>89</v>
+      </c>
+      <c r="H174" s="2" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="175" ht="14.25" customHeight="1">
       <c r="A175" s="2" t="s">
-        <v>97</v>
+        <v>312</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>95</v>
+        <v>311</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>586</v>
+        <v>93</v>
+      </c>
+      <c r="H175" s="2" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
       <c r="A176" s="2" t="s">
-        <v>97</v>
+        <v>312</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>95</v>
+        <v>311</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>587</v>
+        <v>99</v>
+      </c>
+      <c r="H176" s="2" t="s">
+        <v>536</v>
       </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
       <c r="A177" s="2" t="s">
-        <v>97</v>
+        <v>312</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>95</v>
+        <v>311</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>54</v>
+        <v>104</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>588</v>
+        <v>104</v>
+      </c>
+      <c r="H177" s="2" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="178" ht="14.25" customHeight="1">
       <c r="A178" s="2" t="s">
-        <v>97</v>
+        <v>312</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>95</v>
+        <v>311</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>589</v>
+        <v>59</v>
+      </c>
+      <c r="H178" s="2" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="179" ht="14.25" customHeight="1">
       <c r="A179" s="2" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>95</v>
+        <v>81</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>537</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>590</v>
+        <v>538</v>
+      </c>
+      <c r="G179" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="H179" s="2" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="180" ht="14.25" customHeight="1">
       <c r="A180" s="2" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>95</v>
+        <v>81</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>537</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>591</v>
+        <v>541</v>
+      </c>
+      <c r="G180" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="H180" s="2" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
       <c r="A181" s="2" t="s">
-        <v>97</v>
+        <v>376</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>95</v>
+        <v>376</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>592</v>
+        <v>50</v>
+      </c>
+      <c r="H181" s="2" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
       <c r="A182" s="2" t="s">
-        <v>97</v>
+        <v>376</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>95</v>
+        <v>376</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>593</v>
+        <v>56</v>
+      </c>
+      <c r="H182" s="2" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
       <c r="A183" s="2" t="s">
-        <v>97</v>
+        <v>376</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>95</v>
+        <v>376</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>594</v>
+        <v>61</v>
+      </c>
+      <c r="H183" s="2" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
       <c r="A184" s="2" t="s">
-        <v>97</v>
+        <v>376</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>95</v>
+        <v>376</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>595</v>
+        <v>65</v>
+      </c>
+      <c r="H184" s="2" t="s">
+        <v>547</v>
       </c>
     </row>
     <row r="185" ht="14.25" customHeight="1">
       <c r="A185" s="2" t="s">
-        <v>97</v>
+        <v>371</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>95</v>
+        <v>371</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>114</v>
+        <v>50</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>596</v>
+        <v>544</v>
       </c>
     </row>
     <row r="186" ht="14.25" customHeight="1">
       <c r="A186" s="2" t="s">
-        <v>97</v>
+        <v>371</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>95</v>
+        <v>371</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>118</v>
+        <v>56</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>597</v>
+        <v>545</v>
       </c>
     </row>
     <row r="187" ht="14.25" customHeight="1">
       <c r="A187" s="2" t="s">
-        <v>97</v>
+        <v>371</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>95</v>
+        <v>371</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>122</v>
+        <v>61</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>598</v>
+        <v>546</v>
       </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
       <c r="A188" s="2" t="s">
-        <v>97</v>
+        <v>371</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>95</v>
+        <v>371</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>126</v>
+        <v>65</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>599</v>
+        <v>547</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
       <c r="A189" s="2" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>101</v>
+        <v>548</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F189" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H189" s="2" t="s">
-        <v>583</v>
+      <c r="F189" s="5" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="190" ht="14.25" customHeight="1">
       <c r="A190" s="2" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>101</v>
+        <v>548</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F190" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H190" s="2" t="s">
-        <v>584</v>
+      <c r="F190" s="5" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="191" ht="14.25" customHeight="1">
       <c r="A191" s="2" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>101</v>
+        <v>548</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>61</v>
+        <v>549</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H191" s="2" t="s">
-        <v>585</v>
+        <v>550</v>
       </c>
     </row>
     <row r="192" ht="14.25" customHeight="1">
       <c r="A192" s="2" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>101</v>
+        <v>551</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>72</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H192" s="2" t="s">
-        <v>586</v>
+        <v>50</v>
+      </c>
+      <c r="H192" s="5" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="193" ht="14.25" customHeight="1">
       <c r="A193" s="2" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>101</v>
+        <v>551</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>72</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H193" s="2" t="s">
-        <v>587</v>
+        <v>56</v>
+      </c>
+      <c r="H193" s="5" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="194" ht="14.25" customHeight="1">
       <c r="A194" s="2" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>101</v>
+        <v>551</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>72</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>54</v>
+        <v>549</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>54</v>
+        <v>549</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>588</v>
+        <v>550</v>
       </c>
     </row>
     <row r="195" ht="14.25" customHeight="1">
       <c r="A195" s="2" t="s">
-        <v>102</v>
+        <v>552</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>101</v>
+        <v>553</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>554</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>79</v>
+        <v>555</v>
+      </c>
+      <c r="G195" s="2" t="s">
+        <v>556</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>589</v>
+        <v>26</v>
       </c>
     </row>
     <row r="196" ht="14.25" customHeight="1">
       <c r="A196" s="2" t="s">
-        <v>102</v>
+        <v>552</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>101</v>
+        <v>553</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>554</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>73</v>
+        <v>34</v>
+      </c>
+      <c r="G196" s="2" t="s">
+        <v>557</v>
       </c>
       <c r="H196" s="2" t="s">
-        <v>590</v>
+        <v>558</v>
       </c>
     </row>
     <row r="197" ht="14.25" customHeight="1">
       <c r="A197" s="2" t="s">
-        <v>102</v>
+        <v>552</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>101</v>
+        <v>553</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>554</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>89</v>
+        <v>559</v>
+      </c>
+      <c r="G197" s="2" t="s">
+        <v>526</v>
       </c>
       <c r="H197" s="2" t="s">
-        <v>591</v>
+        <v>547</v>
       </c>
     </row>
     <row r="198" ht="14.25" customHeight="1">
       <c r="A198" s="2" t="s">
-        <v>102</v>
+        <v>552</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>101</v>
+        <v>553</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>554</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>93</v>
+        <v>560</v>
+      </c>
+      <c r="G198" s="2" t="s">
+        <v>561</v>
       </c>
       <c r="H198" s="2" t="s">
-        <v>592</v>
+        <v>25</v>
       </c>
     </row>
     <row r="199" ht="14.25" customHeight="1">
       <c r="A199" s="2" t="s">
-        <v>102</v>
+        <v>346</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>101</v>
+        <v>562</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>554</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>99</v>
+        <v>560</v>
       </c>
       <c r="H199" s="2" t="s">
-        <v>593</v>
+        <v>25</v>
       </c>
     </row>
     <row r="200" ht="14.25" customHeight="1">
-      <c r="A200" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B200" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D200" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E200" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F200" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H200" s="2" t="s">
-        <v>594</v>
+      <c r="A200" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="B200" s="8" t="s">
+        <v>563</v>
+      </c>
+      <c r="C200" s="8"/>
+      <c r="D200" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E200" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F200" s="8" t="s">
+        <v>560</v>
+      </c>
+      <c r="G200" s="8" t="s">
+        <v>561</v>
+      </c>
+      <c r="H200" s="8" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="201" ht="14.25" customHeight="1">
-      <c r="A201" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B201" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D201" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E201" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F201" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H201" s="2" t="s">
-        <v>595</v>
+      <c r="A201" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="B201" s="8" t="s">
+        <v>563</v>
+      </c>
+      <c r="C201" s="8"/>
+      <c r="D201" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E201" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F201" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="G201" s="8" t="s">
+        <v>556</v>
+      </c>
+      <c r="H201" s="8" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="202" ht="14.25" customHeight="1">
-      <c r="A202" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B202" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D202" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E202" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F202" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="H202" s="2" t="s">
-        <v>596</v>
+      <c r="A202" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="B202" s="7" t="s">
+        <v>564</v>
+      </c>
+      <c r="C202" s="8"/>
+      <c r="D202" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E202" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="F202" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="G202" s="8"/>
+      <c r="H202" s="7" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
-      <c r="A203" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B203" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D203" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E203" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="F203" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H203" s="2" t="s">
-        <v>597</v>
+      <c r="A203" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="B203" s="7" t="s">
+        <v>564</v>
+      </c>
+      <c r="C203" s="8"/>
+      <c r="D203" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E203" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="F203" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="G203" s="8"/>
+      <c r="H203" s="7" t="s">
+        <v>566</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
-      <c r="A204" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B204" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D204" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E204" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="F204" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H204" s="2" t="s">
-        <v>598</v>
+      <c r="A204" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="B204" s="7" t="s">
+        <v>567</v>
+      </c>
+      <c r="C204" s="8"/>
+      <c r="D204" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E204" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="F204" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="G204" s="8"/>
+      <c r="H204" s="7" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="205" ht="14.25" customHeight="1">
-      <c r="A205" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B205" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D205" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E205" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="F205" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="H205" s="2" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="206" ht="14.25" customHeight="1">
-      <c r="A206" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="B206" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="D206" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E206" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F206" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H206" s="2" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="207" ht="14.25" customHeight="1">
-      <c r="A207" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="B207" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="D207" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E207" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F207" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H207" s="2" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="208" ht="14.25" customHeight="1">
-      <c r="A208" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="B208" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="D208" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E208" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F208" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H208" s="2" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="209" ht="14.25" customHeight="1">
-      <c r="A209" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="B209" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="D209" s="2" t="s">
+      <c r="A205" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="B205" s="7" t="s">
+        <v>567</v>
+      </c>
+      <c r="C205" s="8"/>
+      <c r="D205" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E209" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F209" s="2" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="210" ht="14.25" customHeight="1">
-      <c r="A210" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="B210" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="D210" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E210" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F210" s="2" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="211" ht="14.25" customHeight="1">
-      <c r="A211" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="B211" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="D211" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E211" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F211" s="2" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="212" ht="14.25" customHeight="1">
-      <c r="A212" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="B212" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="D212" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E212" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F212" s="2" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="213" ht="14.25" customHeight="1">
-      <c r="A213" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="B213" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="D213" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E213" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F213" s="2" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="214" ht="14.25" customHeight="1">
-      <c r="A214" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="B214" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="D214" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E214" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F214" s="2" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="215" ht="14.25" customHeight="1">
-      <c r="A215" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="B215" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="D215" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E215" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F215" s="2" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="216" ht="14.25" customHeight="1">
-      <c r="A216" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="B216" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="D216" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E216" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F216" s="2" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="217" ht="14.25" customHeight="1">
-      <c r="A217" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B217" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="C217" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="D217" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E217" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F217" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="G217" s="2" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="218" ht="14.25" customHeight="1">
-      <c r="A218" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B218" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="C218" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="D218" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E218" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F218" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="G218" s="2" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="219" ht="14.25" customHeight="1">
-      <c r="A219" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B219" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="C219" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="D219" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E219" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F219" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="G219" s="2" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="220" ht="14.25" customHeight="1">
-      <c r="A220" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B220" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="C220" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="D220" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E220" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F220" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="G220" s="2" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="221" ht="14.25" customHeight="1">
-      <c r="A221" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="B221" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="D221" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E221" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F221" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H221" s="2" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="222" ht="14.25" customHeight="1">
-      <c r="A222" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="B222" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="D222" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E222" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F222" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H222" s="2" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="223" ht="14.25" customHeight="1">
-      <c r="A223" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="B223" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="D223" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E223" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F223" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H223" s="2" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="224" ht="14.25" customHeight="1">
-      <c r="A224" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="B224" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="D224" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E224" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F224" s="2" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="225" ht="14.25" customHeight="1">
-      <c r="A225" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="B225" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="D225" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E225" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F225" s="2" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="226" ht="14.25" customHeight="1">
-      <c r="A226" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="B226" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="D226" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E226" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F226" s="2" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="227" ht="14.25" customHeight="1">
-      <c r="A227" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B227" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C227" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="D227" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E227" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F227" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="G227" s="2" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="228" ht="14.25" customHeight="1">
-      <c r="A228" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B228" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C228" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="D228" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E228" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F228" s="2" t="s">
-        <v>623</v>
-      </c>
-      <c r="G228" s="2" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="229" ht="14.25" customHeight="1">
-      <c r="A229" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B229" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C229" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="D229" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E229" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F229" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="G229" s="2" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="230" ht="14.25" customHeight="1">
-      <c r="A230" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B230" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C230" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="D230" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E230" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F230" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="G230" s="2" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="231" ht="14.25" customHeight="1">
-      <c r="A231" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B231" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C231" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="D231" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E231" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F231" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="G231" s="2" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="232" ht="14.25" customHeight="1">
-      <c r="A232" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B232" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C232" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="D232" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E232" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F232" s="2" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="233" ht="14.25" customHeight="1">
-      <c r="A233" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B233" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C233" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="D233" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E233" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F233" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="G233" s="2" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="234" ht="14.25" customHeight="1">
-      <c r="A234" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B234" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C234" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="D234" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E234" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F234" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="G234" s="2" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="235" ht="14.25" customHeight="1">
-      <c r="A235" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="B235" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D235" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E235" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F235" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H235" s="2" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="236" ht="14.25" customHeight="1">
-      <c r="A236" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="B236" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D236" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E236" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F236" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H236" s="2" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="237" ht="14.25" customHeight="1">
-      <c r="A237" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="B237" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D237" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E237" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F237" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H237" s="2" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="238" ht="14.25" customHeight="1">
-      <c r="A238" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="B238" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D238" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E238" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F238" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H238" s="2" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="239" ht="14.25" customHeight="1">
-      <c r="A239" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="B239" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D239" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E239" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F239" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H239" s="2" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="240" ht="14.25" customHeight="1">
-      <c r="A240" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="B240" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D240" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E240" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F240" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H240" s="2" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="241" ht="14.25" customHeight="1">
-      <c r="A241" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="B241" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D241" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E241" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F241" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H241" s="2" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="242" ht="14.25" customHeight="1">
-      <c r="A242" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="B242" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D242" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E242" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F242" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H242" s="2" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="243" ht="14.25" customHeight="1">
-      <c r="A243" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="B243" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D243" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E243" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F243" s="2" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="244" ht="14.25" customHeight="1">
-      <c r="A244" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="B244" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D244" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E244" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F244" s="2" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="245" ht="14.25" customHeight="1">
-      <c r="A245" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="B245" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D245" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E245" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F245" s="2" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="246" ht="14.25" customHeight="1">
-      <c r="A246" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="B246" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D246" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E246" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F246" s="2" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="247" ht="14.25" customHeight="1">
-      <c r="A247" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="B247" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D247" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E247" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F247" s="2" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="248" ht="14.25" customHeight="1">
-      <c r="A248" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="B248" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D248" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E248" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F248" s="2" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="249" ht="14.25" customHeight="1">
-      <c r="A249" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="B249" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D249" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E249" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F249" s="2" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="250" ht="14.25" customHeight="1">
-      <c r="A250" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="B250" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D250" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E250" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F250" s="2" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="251" ht="14.25" customHeight="1">
-      <c r="A251" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="B251" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D251" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E251" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F251" s="2" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="252" ht="14.25" customHeight="1">
-      <c r="A252" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="B252" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D252" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E252" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F252" s="2" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="253" ht="14.25" customHeight="1">
-      <c r="A253" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="B253" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D253" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E253" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F253" s="2" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="254" ht="14.25" customHeight="1">
-      <c r="A254" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="B254" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D254" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E254" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F254" s="2" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="255" ht="14.25" customHeight="1">
-      <c r="A255" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="B255" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D255" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E255" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F255" s="2" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="256" ht="14.25" customHeight="1">
-      <c r="A256" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="B256" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="D256" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E256" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F256" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H256" s="2" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="257" ht="14.25" customHeight="1">
-      <c r="A257" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="B257" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="D257" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E257" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F257" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H257" s="2" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="258" ht="14.25" customHeight="1">
-      <c r="A258" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="B258" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="D258" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E258" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F258" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H258" s="2" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="259" ht="14.25" customHeight="1">
-      <c r="A259" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="B259" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="D259" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E259" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F259" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H259" s="2" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="260" ht="14.25" customHeight="1">
-      <c r="A260" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="B260" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="D260" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E260" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F260" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H260" s="2" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="261" ht="14.25" customHeight="1">
-      <c r="A261" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="B261" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="D261" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E261" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F261" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H261" s="2" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="262" ht="14.25" customHeight="1">
-      <c r="A262" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="B262" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="D262" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E262" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F262" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H262" s="2" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="263" ht="14.25" customHeight="1">
-      <c r="A263" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="B263" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="D263" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E263" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F263" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H263" s="2" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="264" ht="14.25" customHeight="1">
-      <c r="A264" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="B264" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="D264" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E264" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F264" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H264" s="2" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="265" ht="14.25" customHeight="1">
-      <c r="A265" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="B265" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="D265" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E265" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F265" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H265" s="2" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="266" ht="14.25" customHeight="1">
-      <c r="A266" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="B266" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="D266" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E266" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F266" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H266" s="2" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="267" ht="14.25" customHeight="1">
-      <c r="A267" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="B267" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="D267" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E267" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F267" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H267" s="2" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="268" ht="14.25" customHeight="1">
-      <c r="A268" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="B268" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="D268" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E268" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F268" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H268" s="2" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="269" ht="14.25" customHeight="1">
-      <c r="A269" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B269" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C269" s="2" t="s">
-        <v>629</v>
-      </c>
-      <c r="D269" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E269" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F269" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="G269" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="H269" s="2" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="270" ht="14.25" customHeight="1">
-      <c r="A270" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B270" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C270" s="2" t="s">
-        <v>629</v>
-      </c>
-      <c r="D270" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E270" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F270" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="G270" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="H270" s="2" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="271" ht="14.25" customHeight="1">
-      <c r="A271" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="B271" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="D271" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E271" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F271" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H271" s="2" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="272" ht="14.25" customHeight="1">
-      <c r="A272" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="B272" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="D272" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E272" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F272" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H272" s="2" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="273" ht="14.25" customHeight="1">
-      <c r="A273" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="B273" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="D273" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E273" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F273" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H273" s="2" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="274" ht="14.25" customHeight="1">
-      <c r="A274" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="B274" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="D274" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E274" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F274" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H274" s="2" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="275" ht="14.25" customHeight="1">
-      <c r="A275" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="B275" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="D275" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E275" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F275" s="2" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="276" ht="14.25" customHeight="1">
-      <c r="A276" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="B276" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="D276" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E276" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F276" s="2" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="277" ht="14.25" customHeight="1">
-      <c r="A277" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="B277" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="D277" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E277" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F277" s="2" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="278" ht="14.25" customHeight="1">
-      <c r="A278" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="B278" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="D278" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E278" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F278" s="2" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="279" ht="14.25" customHeight="1">
-      <c r="A279" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B279" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="D279" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E279" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F279" s="5" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="280" ht="14.25" customHeight="1">
-      <c r="A280" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B280" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="D280" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E280" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F280" s="5" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="281" ht="14.25" customHeight="1">
-      <c r="A281" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B281" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="D281" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E281" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="F281" s="2" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="282" ht="14.25" customHeight="1">
-      <c r="A282" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B282" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="D282" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E282" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F282" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H282" s="5" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="283" ht="14.25" customHeight="1">
-      <c r="A283" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B283" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="D283" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E283" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F283" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H283" s="5" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="284" ht="14.25" customHeight="1">
-      <c r="A284" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B284" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="D284" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E284" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="F284" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="H284" s="2" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="285" ht="14.25" customHeight="1">
-      <c r="A285" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="B285" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="C285" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="D285" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E285" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F285" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="G285" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="H285" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="286" ht="14.25" customHeight="1">
-      <c r="A286" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="B286" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="C286" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="D286" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E286" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F286" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G286" s="2" t="s">
-        <v>651</v>
-      </c>
-      <c r="H286" s="2" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="287" ht="14.25" customHeight="1">
-      <c r="A287" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="B287" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="C287" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="D287" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E287" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F287" s="2" t="s">
-        <v>653</v>
-      </c>
-      <c r="G287" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="H287" s="2" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="288" ht="14.25" customHeight="1">
-      <c r="A288" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="B288" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="C288" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="D288" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E288" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F288" s="2" t="s">
-        <v>654</v>
-      </c>
-      <c r="G288" s="2" t="s">
-        <v>655</v>
-      </c>
-      <c r="H288" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="289" ht="14.25" customHeight="1">
-      <c r="A289" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="B289" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="C289" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="D289" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E289" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F289" s="2" t="s">
-        <v>654</v>
-      </c>
-      <c r="H289" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="290" ht="14.25" customHeight="1">
-      <c r="A290" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="B290" s="8" t="s">
-        <v>657</v>
-      </c>
-      <c r="C290" s="8"/>
-      <c r="D290" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E290" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="F290" s="8" t="s">
-        <v>654</v>
-      </c>
-      <c r="G290" s="8" t="s">
-        <v>655</v>
-      </c>
-      <c r="H290" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="291" ht="14.25" customHeight="1">
-      <c r="A291" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="B291" s="8" t="s">
-        <v>657</v>
-      </c>
-      <c r="C291" s="8"/>
-      <c r="D291" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E291" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F291" s="8" t="s">
-        <v>649</v>
-      </c>
-      <c r="G291" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="H291" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="292" ht="14.25" customHeight="1">
-      <c r="A292" s="7" t="s">
-        <v>416</v>
-      </c>
-      <c r="B292" s="7" t="s">
-        <v>658</v>
-      </c>
-      <c r="C292" s="8"/>
-      <c r="D292" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E292" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="F292" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="G292" s="8"/>
-      <c r="H292" s="7" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="293" ht="14.25" customHeight="1">
-      <c r="A293" s="7" t="s">
-        <v>416</v>
-      </c>
-      <c r="B293" s="7" t="s">
-        <v>658</v>
-      </c>
-      <c r="C293" s="8"/>
-      <c r="D293" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E293" s="7">
+      <c r="E205" s="7">
         <v>2.0</v>
       </c>
-      <c r="F293" s="7">
+      <c r="F205" s="7">
         <v>2.0</v>
       </c>
-      <c r="G293" s="8"/>
-      <c r="H293" s="7" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="294" ht="14.25" customHeight="1">
-      <c r="A294" s="7" t="s">
-        <v>418</v>
-      </c>
-      <c r="B294" s="7" t="s">
-        <v>661</v>
-      </c>
-      <c r="C294" s="8"/>
-      <c r="D294" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E294" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="F294" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="G294" s="8"/>
-      <c r="H294" s="7" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="295" ht="14.25" customHeight="1">
-      <c r="A295" s="7" t="s">
-        <v>418</v>
-      </c>
-      <c r="B295" s="7" t="s">
-        <v>661</v>
-      </c>
-      <c r="C295" s="8"/>
-      <c r="D295" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E295" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="F295" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="G295" s="8"/>
-      <c r="H295" s="7" t="s">
-        <v>660</v>
-      </c>
-    </row>
+      <c r="G205" s="8"/>
+      <c r="H205" s="7" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="206" ht="14.25" customHeight="1"/>
+    <row r="207" ht="14.25" customHeight="1"/>
+    <row r="208" ht="14.25" customHeight="1"/>
+    <row r="209" ht="14.25" customHeight="1"/>
+    <row r="210" ht="14.25" customHeight="1"/>
+    <row r="211" ht="14.25" customHeight="1"/>
+    <row r="212" ht="14.25" customHeight="1"/>
+    <row r="213" ht="14.25" customHeight="1"/>
+    <row r="214" ht="14.25" customHeight="1"/>
+    <row r="215" ht="14.25" customHeight="1"/>
+    <row r="216" ht="14.25" customHeight="1"/>
+    <row r="217" ht="14.25" customHeight="1"/>
+    <row r="218" ht="14.25" customHeight="1"/>
+    <row r="219" ht="14.25" customHeight="1"/>
+    <row r="220" ht="14.25" customHeight="1"/>
+    <row r="221" ht="14.25" customHeight="1"/>
+    <row r="222" ht="14.25" customHeight="1"/>
+    <row r="223" ht="14.25" customHeight="1"/>
+    <row r="224" ht="14.25" customHeight="1"/>
+    <row r="225" ht="14.25" customHeight="1"/>
+    <row r="226" ht="14.25" customHeight="1"/>
+    <row r="227" ht="14.25" customHeight="1"/>
+    <row r="228" ht="14.25" customHeight="1"/>
+    <row r="229" ht="14.25" customHeight="1"/>
+    <row r="230" ht="14.25" customHeight="1"/>
+    <row r="231" ht="14.25" customHeight="1"/>
+    <row r="232" ht="14.25" customHeight="1"/>
+    <row r="233" ht="14.25" customHeight="1"/>
+    <row r="234" ht="14.25" customHeight="1"/>
+    <row r="235" ht="14.25" customHeight="1"/>
+    <row r="236" ht="14.25" customHeight="1"/>
+    <row r="237" ht="14.25" customHeight="1"/>
+    <row r="238" ht="14.25" customHeight="1"/>
+    <row r="239" ht="14.25" customHeight="1"/>
+    <row r="240" ht="14.25" customHeight="1"/>
+    <row r="241" ht="14.25" customHeight="1"/>
+    <row r="242" ht="14.25" customHeight="1"/>
+    <row r="243" ht="14.25" customHeight="1"/>
+    <row r="244" ht="14.25" customHeight="1"/>
+    <row r="245" ht="14.25" customHeight="1"/>
+    <row r="246" ht="14.25" customHeight="1"/>
+    <row r="247" ht="14.25" customHeight="1"/>
+    <row r="248" ht="14.25" customHeight="1"/>
+    <row r="249" ht="14.25" customHeight="1"/>
+    <row r="250" ht="14.25" customHeight="1"/>
+    <row r="251" ht="14.25" customHeight="1"/>
+    <row r="252" ht="14.25" customHeight="1"/>
+    <row r="253" ht="14.25" customHeight="1"/>
+    <row r="254" ht="14.25" customHeight="1"/>
+    <row r="255" ht="14.25" customHeight="1"/>
+    <row r="256" ht="14.25" customHeight="1"/>
+    <row r="257" ht="14.25" customHeight="1"/>
+    <row r="258" ht="14.25" customHeight="1"/>
+    <row r="259" ht="14.25" customHeight="1"/>
+    <row r="260" ht="14.25" customHeight="1"/>
+    <row r="261" ht="14.25" customHeight="1"/>
+    <row r="262" ht="14.25" customHeight="1"/>
+    <row r="263" ht="14.25" customHeight="1"/>
+    <row r="264" ht="14.25" customHeight="1"/>
+    <row r="265" ht="14.25" customHeight="1"/>
+    <row r="266" ht="14.25" customHeight="1"/>
+    <row r="267" ht="14.25" customHeight="1"/>
+    <row r="268" ht="14.25" customHeight="1"/>
+    <row r="269" ht="14.25" customHeight="1"/>
+    <row r="270" ht="14.25" customHeight="1"/>
+    <row r="271" ht="14.25" customHeight="1"/>
+    <row r="272" ht="14.25" customHeight="1"/>
+    <row r="273" ht="14.25" customHeight="1"/>
+    <row r="274" ht="14.25" customHeight="1"/>
+    <row r="275" ht="14.25" customHeight="1"/>
+    <row r="276" ht="14.25" customHeight="1"/>
+    <row r="277" ht="14.25" customHeight="1"/>
+    <row r="278" ht="14.25" customHeight="1"/>
+    <row r="279" ht="14.25" customHeight="1"/>
+    <row r="280" ht="14.25" customHeight="1"/>
+    <row r="281" ht="14.25" customHeight="1"/>
+    <row r="282" ht="14.25" customHeight="1"/>
+    <row r="283" ht="14.25" customHeight="1"/>
+    <row r="284" ht="14.25" customHeight="1"/>
+    <row r="285" ht="14.25" customHeight="1"/>
+    <row r="286" ht="14.25" customHeight="1"/>
+    <row r="287" ht="14.25" customHeight="1"/>
+    <row r="288" ht="14.25" customHeight="1"/>
+    <row r="289" ht="14.25" customHeight="1"/>
+    <row r="290" ht="14.25" customHeight="1"/>
+    <row r="291" ht="14.25" customHeight="1"/>
+    <row r="292" ht="14.25" customHeight="1"/>
+    <row r="293" ht="14.25" customHeight="1"/>
+    <row r="294" ht="14.25" customHeight="1"/>
+    <row r="295" ht="14.25" customHeight="1"/>
     <row r="296" ht="14.25" customHeight="1"/>
     <row r="297" ht="14.25" customHeight="1"/>
     <row r="298" ht="14.25" customHeight="1"/>
@@ -17049,98 +15192,8 @@
     <row r="877" ht="14.25" customHeight="1"/>
     <row r="878" ht="14.25" customHeight="1"/>
     <row r="879" ht="14.25" customHeight="1"/>
-    <row r="880" ht="14.25" customHeight="1"/>
-    <row r="881" ht="14.25" customHeight="1"/>
-    <row r="882" ht="14.25" customHeight="1"/>
-    <row r="883" ht="14.25" customHeight="1"/>
-    <row r="884" ht="14.25" customHeight="1"/>
-    <row r="885" ht="14.25" customHeight="1"/>
-    <row r="886" ht="14.25" customHeight="1"/>
-    <row r="887" ht="14.25" customHeight="1"/>
-    <row r="888" ht="14.25" customHeight="1"/>
-    <row r="889" ht="14.25" customHeight="1"/>
-    <row r="890" ht="14.25" customHeight="1"/>
-    <row r="891" ht="14.25" customHeight="1"/>
-    <row r="892" ht="14.25" customHeight="1"/>
-    <row r="893" ht="14.25" customHeight="1"/>
-    <row r="894" ht="14.25" customHeight="1"/>
-    <row r="895" ht="14.25" customHeight="1"/>
-    <row r="896" ht="14.25" customHeight="1"/>
-    <row r="897" ht="14.25" customHeight="1"/>
-    <row r="898" ht="14.25" customHeight="1"/>
-    <row r="899" ht="14.25" customHeight="1"/>
-    <row r="900" ht="14.25" customHeight="1"/>
-    <row r="901" ht="14.25" customHeight="1"/>
-    <row r="902" ht="14.25" customHeight="1"/>
-    <row r="903" ht="14.25" customHeight="1"/>
-    <row r="904" ht="14.25" customHeight="1"/>
-    <row r="905" ht="14.25" customHeight="1"/>
-    <row r="906" ht="14.25" customHeight="1"/>
-    <row r="907" ht="14.25" customHeight="1"/>
-    <row r="908" ht="14.25" customHeight="1"/>
-    <row r="909" ht="14.25" customHeight="1"/>
-    <row r="910" ht="14.25" customHeight="1"/>
-    <row r="911" ht="14.25" customHeight="1"/>
-    <row r="912" ht="14.25" customHeight="1"/>
-    <row r="913" ht="14.25" customHeight="1"/>
-    <row r="914" ht="14.25" customHeight="1"/>
-    <row r="915" ht="14.25" customHeight="1"/>
-    <row r="916" ht="14.25" customHeight="1"/>
-    <row r="917" ht="14.25" customHeight="1"/>
-    <row r="918" ht="14.25" customHeight="1"/>
-    <row r="919" ht="14.25" customHeight="1"/>
-    <row r="920" ht="14.25" customHeight="1"/>
-    <row r="921" ht="14.25" customHeight="1"/>
-    <row r="922" ht="14.25" customHeight="1"/>
-    <row r="923" ht="14.25" customHeight="1"/>
-    <row r="924" ht="14.25" customHeight="1"/>
-    <row r="925" ht="14.25" customHeight="1"/>
-    <row r="926" ht="14.25" customHeight="1"/>
-    <row r="927" ht="14.25" customHeight="1"/>
-    <row r="928" ht="14.25" customHeight="1"/>
-    <row r="929" ht="14.25" customHeight="1"/>
-    <row r="930" ht="14.25" customHeight="1"/>
-    <row r="931" ht="14.25" customHeight="1"/>
-    <row r="932" ht="14.25" customHeight="1"/>
-    <row r="933" ht="14.25" customHeight="1"/>
-    <row r="934" ht="14.25" customHeight="1"/>
-    <row r="935" ht="14.25" customHeight="1"/>
-    <row r="936" ht="14.25" customHeight="1"/>
-    <row r="937" ht="14.25" customHeight="1"/>
-    <row r="938" ht="14.25" customHeight="1"/>
-    <row r="939" ht="14.25" customHeight="1"/>
-    <row r="940" ht="14.25" customHeight="1"/>
-    <row r="941" ht="14.25" customHeight="1"/>
-    <row r="942" ht="14.25" customHeight="1"/>
-    <row r="943" ht="14.25" customHeight="1"/>
-    <row r="944" ht="14.25" customHeight="1"/>
-    <row r="945" ht="14.25" customHeight="1"/>
-    <row r="946" ht="14.25" customHeight="1"/>
-    <row r="947" ht="14.25" customHeight="1"/>
-    <row r="948" ht="14.25" customHeight="1"/>
-    <row r="949" ht="14.25" customHeight="1"/>
-    <row r="950" ht="14.25" customHeight="1"/>
-    <row r="951" ht="14.25" customHeight="1"/>
-    <row r="952" ht="14.25" customHeight="1"/>
-    <row r="953" ht="14.25" customHeight="1"/>
-    <row r="954" ht="14.25" customHeight="1"/>
-    <row r="955" ht="14.25" customHeight="1"/>
-    <row r="956" ht="14.25" customHeight="1"/>
-    <row r="957" ht="14.25" customHeight="1"/>
-    <row r="958" ht="14.25" customHeight="1"/>
-    <row r="959" ht="14.25" customHeight="1"/>
-    <row r="960" ht="14.25" customHeight="1"/>
-    <row r="961" ht="14.25" customHeight="1"/>
-    <row r="962" ht="14.25" customHeight="1"/>
-    <row r="963" ht="14.25" customHeight="1"/>
-    <row r="964" ht="14.25" customHeight="1"/>
-    <row r="965" ht="14.25" customHeight="1"/>
-    <row r="966" ht="14.25" customHeight="1"/>
-    <row r="967" ht="14.25" customHeight="1"/>
-    <row r="968" ht="14.25" customHeight="1"/>
-    <row r="969" ht="14.25" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="$A$1:$H$295"/>
+  <autoFilter ref="$A$1:$H$205"/>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
@@ -17172,61 +15225,61 @@
         <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>662</v>
+        <v>568</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>663</v>
+        <v>569</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>664</v>
+        <v>570</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>665</v>
+        <v>571</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>664</v>
+        <v>570</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>666</v>
+        <v>572</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>667</v>
+        <v>573</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>668</v>
+        <v>574</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>667</v>
+        <v>573</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>669</v>
+        <v>575</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>670</v>
+        <v>576</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>671</v>
+        <v>577</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>670</v>
+        <v>576</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>672</v>
+        <v>578</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1"/>
@@ -18259,19 +16312,19 @@
         <v>422</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>673</v>
+        <v>579</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>674</v>
+        <v>580</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>675</v>
+        <v>581</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>676</v>
+        <v>582</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>677</v>
+        <v>583</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>46</v>
@@ -18282,13 +16335,13 @@
         <v>394</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>678</v>
+        <v>584</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>680</v>
+        <v>586</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
@@ -18296,13 +16349,13 @@
         <v>234</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>681</v>
+        <v>587</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>682</v>
+        <v>588</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
@@ -18310,13 +16363,13 @@
         <v>240</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>683</v>
+        <v>589</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>684</v>
+        <v>590</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
@@ -18324,13 +16377,13 @@
         <v>248</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>685</v>
+        <v>591</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>686</v>
+        <v>592</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
@@ -18338,13 +16391,13 @@
         <v>237</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>687</v>
+        <v>593</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>688</v>
+        <v>594</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
@@ -18352,13 +16405,13 @@
         <v>244</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>689</v>
+        <v>595</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>690</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
@@ -18366,13 +16419,13 @@
         <v>222</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>691</v>
+        <v>597</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>692</v>
+        <v>598</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
@@ -18380,13 +16433,13 @@
         <v>230</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>693</v>
+        <v>599</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>694</v>
+        <v>600</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
@@ -18394,13 +16447,13 @@
         <v>226</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>695</v>
+        <v>601</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>696</v>
+        <v>602</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
@@ -18408,13 +16461,13 @@
         <v>407</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>697</v>
+        <v>603</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>698</v>
+        <v>604</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
@@ -18422,13 +16475,13 @@
         <v>409</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>699</v>
+        <v>605</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>700</v>
+        <v>606</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
@@ -18436,13 +16489,13 @@
         <v>411</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>701</v>
+        <v>607</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>702</v>
+        <v>608</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
@@ -18450,13 +16503,13 @@
         <v>413</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>703</v>
+        <v>609</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>704</v>
+        <v>610</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
@@ -18464,13 +16517,13 @@
         <v>189</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>705</v>
+        <v>611</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>706</v>
+        <v>612</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
@@ -18478,13 +16531,13 @@
         <v>388</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>707</v>
+        <v>613</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>708</v>
+        <v>614</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
@@ -18492,13 +16545,13 @@
         <v>391</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>709</v>
+        <v>615</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>710</v>
+        <v>616</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
@@ -18506,13 +16559,13 @@
         <v>397</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>711</v>
+        <v>617</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>712</v>
+        <v>618</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
@@ -18520,13 +16573,13 @@
         <v>253</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>713</v>
+        <v>619</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>714</v>
+        <v>620</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
@@ -18534,13 +16587,13 @@
         <v>400</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>715</v>
+        <v>621</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>716</v>
+        <v>622</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
@@ -18551,10 +16604,10 @@
         <v>74</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>717</v>
+        <v>623</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
@@ -18562,13 +16615,13 @@
         <v>292</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>718</v>
+        <v>624</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>719</v>
+        <v>625</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
@@ -18576,13 +16629,13 @@
         <v>299</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>720</v>
+        <v>626</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>721</v>
+        <v>627</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
@@ -18593,10 +16646,10 @@
         <v>98</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>722</v>
+        <v>628</v>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1">
@@ -18607,10 +16660,10 @@
         <v>367</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>723</v>
+        <v>629</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
@@ -18618,13 +16671,13 @@
         <v>354</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>724</v>
+        <v>630</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>725</v>
+        <v>631</v>
       </c>
     </row>
     <row r="27" ht="14.25" customHeight="1">
@@ -18632,13 +16685,13 @@
         <v>357</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>726</v>
+        <v>632</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>727</v>
+        <v>633</v>
       </c>
     </row>
     <row r="28" ht="14.25" customHeight="1">
@@ -18649,10 +16702,10 @@
         <v>343</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>728</v>
+        <v>634</v>
       </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
@@ -18663,10 +16716,10 @@
         <v>314</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>729</v>
+        <v>635</v>
       </c>
     </row>
     <row r="30" ht="14.25" customHeight="1">
@@ -18677,10 +16730,10 @@
         <v>121</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>730</v>
+        <v>636</v>
       </c>
     </row>
     <row r="31" ht="14.25" customHeight="1">
@@ -18691,10 +16744,10 @@
         <v>360</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>731</v>
+        <v>637</v>
       </c>
     </row>
     <row r="32" ht="14.25" customHeight="1">
@@ -18705,10 +16758,10 @@
         <v>175</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>732</v>
+        <v>638</v>
       </c>
     </row>
     <row r="33" ht="14.25" customHeight="1">
@@ -18719,10 +16772,10 @@
         <v>309</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>733</v>
+        <v>639</v>
       </c>
     </row>
     <row r="34" ht="14.25" customHeight="1">
@@ -18733,10 +16786,10 @@
         <v>321</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>734</v>
+        <v>640</v>
       </c>
     </row>
     <row r="35" ht="14.25" customHeight="1">
@@ -18747,10 +16800,10 @@
         <v>129</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>735</v>
+        <v>641</v>
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1">
@@ -18761,10 +16814,10 @@
         <v>318</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>736</v>
+        <v>642</v>
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1">
@@ -18775,10 +16828,10 @@
         <v>117</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>737</v>
+        <v>643</v>
       </c>
     </row>
     <row r="38" ht="14.25" customHeight="1">
@@ -18786,13 +16839,13 @@
         <v>380</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>738</v>
+        <v>644</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>739</v>
+        <v>645</v>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
@@ -18800,13 +16853,13 @@
         <v>372</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>740</v>
+        <v>646</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>741</v>
+        <v>647</v>
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1">
@@ -18817,10 +16870,10 @@
         <v>144</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>742</v>
+        <v>648</v>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1">
@@ -18831,10 +16884,10 @@
         <v>135</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>743</v>
+        <v>649</v>
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1">
@@ -18845,10 +16898,10 @@
         <v>167</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>744</v>
+        <v>650</v>
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1">
@@ -18859,10 +16912,10 @@
         <v>171</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>745</v>
+        <v>651</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
@@ -18873,10 +16926,10 @@
         <v>153</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>746</v>
+        <v>652</v>
       </c>
     </row>
     <row r="45" ht="14.25" customHeight="1">
@@ -18887,10 +16940,10 @@
         <v>163</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>747</v>
+        <v>653</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1">
@@ -18901,10 +16954,10 @@
         <v>158</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>748</v>
+        <v>654</v>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
@@ -18915,10 +16968,10 @@
         <v>363</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>749</v>
+        <v>655</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1"/>
@@ -19859,10 +17912,10 @@
         <v>421</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>674</v>
+        <v>580</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>677</v>
+        <v>583</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>46</v>
@@ -19873,7 +17926,7 @@
         <v>402</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>750</v>
+        <v>656</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
@@ -19881,7 +17934,7 @@
         <v>182</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>751</v>
+        <v>657</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
@@ -19889,23 +17942,23 @@
         <v>258</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>752</v>
+        <v>658</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>753</v>
+        <v>659</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>754</v>
+        <v>660</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>755</v>
+        <v>661</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>756</v>
+        <v>662</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1"/>
@@ -20929,21 +18982,21 @@
         <v>421</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>757</v>
+        <v>663</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>758</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>759</v>
+        <v>665</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>760</v>
+        <v>666</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>761</v>
+        <v>667</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1"/>

--- a/tests/testthat/vlm_test_spec.xlsx
+++ b/tests/testthat/vlm_test_spec.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2655" uniqueCount="668">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2662" uniqueCount="669">
   <si>
     <t>Attribute</t>
   </si>
@@ -1412,6 +1412,9 @@
   </si>
   <si>
     <t>Codelist for ADEX.AVISITN</t>
+  </si>
+  <si>
+    <t>70</t>
   </si>
   <si>
     <t>Codelist for ADEX.EXDOSFRM</t>
@@ -2125,7 +2128,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2144,6 +2147,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
@@ -11238,261 +11244,296 @@
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="8" t="s">
         <v>452</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="C36" s="8"/>
+      <c r="D36" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E36" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="F36" s="8" t="s">
         <v>453</v>
       </c>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
     </row>
     <row r="37" ht="14.25" customHeight="1">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="8" t="s">
         <v>452</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="C37" s="8"/>
+      <c r="D37" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E37" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="F37" s="8" t="s">
         <v>454</v>
       </c>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
     </row>
     <row r="38" ht="14.25" customHeight="1">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="8" t="s">
         <v>452</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="C38" s="8"/>
+      <c r="D38" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="E38" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="F38" s="8" t="s">
         <v>455</v>
       </c>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
     </row>
     <row r="39" ht="14.25" customHeight="1">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="8" t="s">
         <v>452</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="C39" s="8"/>
+      <c r="D39" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="E39" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="F39" s="8" t="s">
         <v>456</v>
       </c>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
     </row>
     <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="8" t="s">
         <v>452</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="C40" s="8"/>
+      <c r="D40" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="E40" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="F40" s="2" t="s">
+      <c r="F40" s="8" t="s">
         <v>457</v>
       </c>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
     </row>
     <row r="41" ht="14.25" customHeight="1">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="8" t="s">
         <v>452</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="C41" s="8"/>
+      <c r="D41" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="E41" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F41" s="2" t="s">
+      <c r="F41" s="8" t="s">
         <v>458</v>
       </c>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
     </row>
     <row r="42" ht="14.25" customHeight="1">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="8" t="s">
         <v>452</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="C42" s="8"/>
+      <c r="D42" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E42" s="2" t="s">
+      <c r="E42" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="F42" s="2" t="s">
+      <c r="F42" s="8" t="s">
         <v>459</v>
       </c>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
     </row>
     <row r="43" ht="14.25" customHeight="1">
-      <c r="A43" s="2" t="s">
+      <c r="A43" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="8" t="s">
         <v>460</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="C43" s="8"/>
+      <c r="D43" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="E43" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="F43" s="5">
-        <v>10.0</v>
-      </c>
-      <c r="H43" s="2" t="s">
+      <c r="F43" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8" t="s">
         <v>453</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="8" t="s">
         <v>460</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="C44" s="8"/>
+      <c r="D44" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="E44" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F44" s="5">
-        <v>20.0</v>
-      </c>
-      <c r="H44" s="2" t="s">
+      <c r="F44" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="45" ht="14.25" customHeight="1">
-      <c r="A45" s="2" t="s">
+      <c r="A45" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="8" t="s">
         <v>460</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="C45" s="8"/>
+      <c r="D45" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="E45" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="F45" s="5">
-        <v>30.0</v>
-      </c>
-      <c r="H45" s="2" t="s">
+      <c r="F45" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8" t="s">
         <v>455</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="8" t="s">
         <v>460</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="C46" s="8"/>
+      <c r="D46" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="E46" s="2" t="s">
+      <c r="E46" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="F46" s="5">
-        <v>40.0</v>
-      </c>
-      <c r="H46" s="2" t="s">
+      <c r="F46" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="8" t="s">
         <v>460</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="C47" s="8"/>
+      <c r="D47" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="E47" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="F47" s="5">
-        <v>50.0</v>
-      </c>
-      <c r="H47" s="2" t="s">
+      <c r="F47" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
-      <c r="A48" s="2" t="s">
+      <c r="A48" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="8" t="s">
         <v>460</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="C48" s="8"/>
+      <c r="D48" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="E48" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F48" s="5">
-        <v>60.0</v>
-      </c>
-      <c r="H48" s="2" t="s">
+      <c r="F48" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="G48" s="8"/>
+      <c r="H48" s="8" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="49" ht="14.25" customHeight="1">
-      <c r="A49" s="2" t="s">
+      <c r="A49" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="8" t="s">
         <v>460</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="C49" s="8"/>
+      <c r="D49" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="E49" s="2" t="s">
+      <c r="E49" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="F49" s="5">
-        <v>70.0</v>
-      </c>
-      <c r="H49" s="2" t="s">
+      <c r="F49" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="G49" s="8"/>
+      <c r="H49" s="8" t="s">
         <v>459</v>
       </c>
     </row>
@@ -11501,7 +11542,7 @@
         <v>207</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>53</v>
@@ -11510,7 +11551,7 @@
         <v>50</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="51" ht="14.25" customHeight="1">
@@ -11518,7 +11559,7 @@
         <v>212</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>53</v>
@@ -11527,7 +11568,7 @@
         <v>50</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1">
@@ -11535,7 +11576,7 @@
         <v>202</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>53</v>
@@ -11544,7 +11585,7 @@
         <v>50</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="53" ht="14.25" customHeight="1">
@@ -11552,7 +11593,7 @@
         <v>217</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>53</v>
@@ -11561,7 +11602,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1">
@@ -11569,7 +11610,7 @@
         <v>193</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>53</v>
@@ -11578,7 +11619,7 @@
         <v>50</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="55" ht="14.25" customHeight="1">
@@ -11586,7 +11627,7 @@
         <v>193</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>53</v>
@@ -11595,7 +11636,7 @@
         <v>56</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="56" ht="14.25" customHeight="1">
@@ -11603,7 +11644,7 @@
         <v>252</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>53</v>
@@ -11620,7 +11661,7 @@
         <v>252</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>53</v>
@@ -11637,7 +11678,7 @@
         <v>252</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>53</v>
@@ -11646,7 +11687,7 @@
         <v>61</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="59" ht="14.25" customHeight="1">
@@ -11654,7 +11695,7 @@
         <v>252</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>53</v>
@@ -11663,7 +11704,7 @@
         <v>65</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="60" ht="14.25" customHeight="1">
@@ -11671,7 +11712,7 @@
         <v>252</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>53</v>
@@ -11688,7 +11729,7 @@
         <v>257</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>53</v>
@@ -11708,7 +11749,7 @@
         <v>257</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>53</v>
@@ -11717,7 +11758,7 @@
         <v>56</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>393</v>
@@ -11728,7 +11769,7 @@
         <v>257</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>53</v>
@@ -11737,10 +11778,10 @@
         <v>61</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="64" ht="14.25" customHeight="1">
@@ -11748,7 +11789,7 @@
         <v>257</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>53</v>
@@ -11757,10 +11798,10 @@
         <v>65</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="65" ht="14.25" customHeight="1">
@@ -11768,7 +11809,7 @@
         <v>257</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>53</v>
@@ -11777,7 +11818,7 @@
         <v>69</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>399</v>
@@ -11788,7 +11829,7 @@
         <v>262</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>72</v>
@@ -11808,7 +11849,7 @@
         <v>262</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>72</v>
@@ -11828,7 +11869,7 @@
         <v>262</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>72</v>
@@ -11840,7 +11881,7 @@
         <v>61</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
@@ -11848,7 +11889,7 @@
         <v>262</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>72</v>
@@ -11860,7 +11901,7 @@
         <v>65</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="70" ht="14.25" customHeight="1">
@@ -11868,7 +11909,7 @@
         <v>262</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>72</v>
@@ -11897,7 +11938,7 @@
         <v>50</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1">
@@ -11914,7 +11955,7 @@
         <v>56</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
@@ -11931,7 +11972,7 @@
         <v>61</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="74" ht="14.25" customHeight="1">
@@ -11951,7 +11992,7 @@
         <v>50</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="75" ht="14.25" customHeight="1">
@@ -11971,7 +12012,7 @@
         <v>56</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="76" ht="14.25" customHeight="1">
@@ -11991,7 +12032,7 @@
         <v>61</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
@@ -12008,7 +12049,7 @@
         <v>50</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
@@ -12025,7 +12066,7 @@
         <v>56</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="79" ht="14.25" customHeight="1">
@@ -12045,7 +12086,7 @@
         <v>50</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="80" ht="14.25" customHeight="1">
@@ -12065,7 +12106,7 @@
         <v>56</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
@@ -12073,10 +12114,10 @@
         <v>77</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>53</v>
@@ -12085,13 +12126,13 @@
         <v>69</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
@@ -12108,7 +12149,7 @@
         <v>50</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="83" ht="14.25" customHeight="1">
@@ -12125,7 +12166,7 @@
         <v>56</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="84" ht="14.25" customHeight="1">
@@ -12142,7 +12183,7 @@
         <v>61</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="85" ht="14.25" customHeight="1">
@@ -12159,7 +12200,7 @@
         <v>65</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
@@ -12176,7 +12217,7 @@
         <v>69</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
@@ -12193,7 +12234,7 @@
         <v>54</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="88" ht="14.25" customHeight="1">
@@ -12210,7 +12251,7 @@
         <v>79</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="89" ht="14.25" customHeight="1">
@@ -12227,7 +12268,7 @@
         <v>73</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="90" ht="14.25" customHeight="1">
@@ -12244,7 +12285,7 @@
         <v>89</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
@@ -12261,7 +12302,7 @@
         <v>93</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="92" ht="14.25" customHeight="1">
@@ -12278,7 +12319,7 @@
         <v>99</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="93" ht="14.25" customHeight="1">
@@ -12295,7 +12336,7 @@
         <v>104</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="94" ht="14.25" customHeight="1">
@@ -12312,7 +12353,7 @@
         <v>59</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="95" ht="14.25" customHeight="1">
@@ -12329,7 +12370,7 @@
         <v>114</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="96" ht="14.25" customHeight="1">
@@ -12346,7 +12387,7 @@
         <v>118</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
@@ -12363,7 +12404,7 @@
         <v>122</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
@@ -12380,7 +12421,7 @@
         <v>126</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="99" ht="14.25" customHeight="1">
@@ -12400,7 +12441,7 @@
         <v>50</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="100" ht="14.25" customHeight="1">
@@ -12420,7 +12461,7 @@
         <v>56</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="101" ht="14.25" customHeight="1">
@@ -12440,7 +12481,7 @@
         <v>61</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="102" ht="14.25" customHeight="1">
@@ -12460,7 +12501,7 @@
         <v>65</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
@@ -12480,7 +12521,7 @@
         <v>69</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="104" ht="14.25" customHeight="1">
@@ -12500,7 +12541,7 @@
         <v>54</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="105" ht="14.25" customHeight="1">
@@ -12520,7 +12561,7 @@
         <v>79</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="106" ht="14.25" customHeight="1">
@@ -12540,7 +12581,7 @@
         <v>73</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="107" ht="14.25" customHeight="1">
@@ -12560,7 +12601,7 @@
         <v>89</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
@@ -12580,7 +12621,7 @@
         <v>93</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
@@ -12600,7 +12641,7 @@
         <v>99</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="110" ht="14.25" customHeight="1">
@@ -12620,7 +12661,7 @@
         <v>104</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="111" ht="14.25" customHeight="1">
@@ -12640,7 +12681,7 @@
         <v>59</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
@@ -12660,7 +12701,7 @@
         <v>114</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="113" ht="14.25" customHeight="1">
@@ -12680,7 +12721,7 @@
         <v>118</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="114" ht="14.25" customHeight="1">
@@ -12700,7 +12741,7 @@
         <v>122</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="115" ht="14.25" customHeight="1">
@@ -12720,15 +12761,15 @@
         <v>126</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="116" ht="14.25" customHeight="1">
       <c r="A116" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>72</v>
@@ -12740,15 +12781,15 @@
         <v>50</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
       <c r="A117" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>72</v>
@@ -12760,15 +12801,15 @@
         <v>56</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
       <c r="A118" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>72</v>
@@ -12780,15 +12821,15 @@
         <v>61</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="119" ht="14.25" customHeight="1">
       <c r="A119" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>53</v>
@@ -12797,15 +12838,15 @@
         <v>50</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="120" ht="14.25" customHeight="1">
       <c r="A120" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>53</v>
@@ -12814,15 +12855,15 @@
         <v>56</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="121" ht="14.25" customHeight="1">
       <c r="A121" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>53</v>
@@ -12831,15 +12872,15 @@
         <v>61</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="122" ht="14.25" customHeight="1">
       <c r="A122" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>53</v>
@@ -12848,15 +12889,15 @@
         <v>50</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="123" ht="14.25" customHeight="1">
       <c r="A123" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>53</v>
@@ -12865,15 +12906,15 @@
         <v>56</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="124" ht="14.25" customHeight="1">
       <c r="A124" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>53</v>
@@ -12882,15 +12923,15 @@
         <v>61</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="125" ht="14.25" customHeight="1">
       <c r="A125" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>53</v>
@@ -12899,15 +12940,15 @@
         <v>65</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="126" ht="14.25" customHeight="1">
       <c r="A126" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>53</v>
@@ -12916,7 +12957,7 @@
         <v>69</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
@@ -12924,10 +12965,10 @@
         <v>108</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>53</v>
@@ -12936,10 +12977,10 @@
         <v>50</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="128" ht="14.25" customHeight="1">
@@ -12947,10 +12988,10 @@
         <v>108</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>53</v>
@@ -12959,10 +13000,10 @@
         <v>56</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="129" ht="14.25" customHeight="1">
@@ -12970,10 +13011,10 @@
         <v>108</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>53</v>
@@ -12982,10 +13023,10 @@
         <v>61</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="130" ht="14.25" customHeight="1">
@@ -12993,10 +13034,10 @@
         <v>108</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>53</v>
@@ -13005,18 +13046,18 @@
         <v>65</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="131" ht="14.25" customHeight="1">
       <c r="A131" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>72</v>
@@ -13028,15 +13069,15 @@
         <v>50</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="132" ht="14.25" customHeight="1">
       <c r="A132" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>72</v>
@@ -13048,15 +13089,15 @@
         <v>56</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="133" ht="14.25" customHeight="1">
       <c r="A133" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>72</v>
@@ -13068,15 +13109,15 @@
         <v>61</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="134" ht="14.25" customHeight="1">
       <c r="A134" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>53</v>
@@ -13085,15 +13126,15 @@
         <v>50</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="135" ht="14.25" customHeight="1">
       <c r="A135" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>53</v>
@@ -13102,15 +13143,15 @@
         <v>56</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="136" ht="14.25" customHeight="1">
       <c r="A136" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>53</v>
@@ -13119,7 +13160,7 @@
         <v>61</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="137" ht="14.25" customHeight="1">
@@ -13130,7 +13171,7 @@
         <v>85</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>53</v>
@@ -13139,10 +13180,10 @@
         <v>50</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
@@ -13153,7 +13194,7 @@
         <v>85</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>53</v>
@@ -13162,10 +13203,10 @@
         <v>56</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="139" ht="14.25" customHeight="1">
@@ -13176,7 +13217,7 @@
         <v>85</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>53</v>
@@ -13185,10 +13226,10 @@
         <v>61</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="140" ht="14.25" customHeight="1">
@@ -13199,7 +13240,7 @@
         <v>85</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>53</v>
@@ -13208,10 +13249,10 @@
         <v>65</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="141" ht="14.25" customHeight="1">
@@ -13222,7 +13263,7 @@
         <v>85</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>53</v>
@@ -13231,10 +13272,10 @@
         <v>69</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
@@ -13245,7 +13286,7 @@
         <v>85</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>53</v>
@@ -13254,7 +13295,7 @@
         <v>54</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
@@ -13265,7 +13306,7 @@
         <v>85</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>53</v>
@@ -13274,10 +13315,10 @@
         <v>79</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="144" ht="14.25" customHeight="1">
@@ -13288,7 +13329,7 @@
         <v>85</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>53</v>
@@ -13297,10 +13338,10 @@
         <v>73</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="145" ht="14.25" customHeight="1">
@@ -13320,7 +13361,7 @@
         <v>50</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="146" ht="14.25" customHeight="1">
@@ -13340,7 +13381,7 @@
         <v>56</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -13360,7 +13401,7 @@
         <v>61</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="148" ht="14.25" customHeight="1">
@@ -13380,7 +13421,7 @@
         <v>65</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
@@ -13400,7 +13441,7 @@
         <v>69</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="150" ht="14.25" customHeight="1">
@@ -13420,7 +13461,7 @@
         <v>54</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="151" ht="14.25" customHeight="1">
@@ -13440,7 +13481,7 @@
         <v>79</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="152" ht="14.25" customHeight="1">
@@ -13460,7 +13501,7 @@
         <v>73</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="153" ht="14.25" customHeight="1">
@@ -13477,7 +13518,7 @@
         <v>50</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="154" ht="14.25" customHeight="1">
@@ -13494,7 +13535,7 @@
         <v>56</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="155" ht="14.25" customHeight="1">
@@ -13511,7 +13552,7 @@
         <v>61</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
@@ -13528,7 +13569,7 @@
         <v>65</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="157" ht="14.25" customHeight="1">
@@ -13545,7 +13586,7 @@
         <v>69</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
@@ -13562,7 +13603,7 @@
         <v>54</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
@@ -13579,7 +13620,7 @@
         <v>79</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="160" ht="14.25" customHeight="1">
@@ -13596,7 +13637,7 @@
         <v>73</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
@@ -13613,7 +13654,7 @@
         <v>89</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
@@ -13630,7 +13671,7 @@
         <v>93</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
@@ -13647,7 +13688,7 @@
         <v>99</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="164" ht="14.25" customHeight="1">
@@ -13664,7 +13705,7 @@
         <v>104</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="165" ht="14.25" customHeight="1">
@@ -13681,7 +13722,7 @@
         <v>59</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
@@ -13701,7 +13742,7 @@
         <v>50</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="167" ht="14.25" customHeight="1">
@@ -13721,7 +13762,7 @@
         <v>56</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="168" ht="14.25" customHeight="1">
@@ -13741,7 +13782,7 @@
         <v>61</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="169" ht="14.25" customHeight="1">
@@ -13761,7 +13802,7 @@
         <v>65</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="170" ht="14.25" customHeight="1">
@@ -13781,7 +13822,7 @@
         <v>69</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
@@ -13801,7 +13842,7 @@
         <v>54</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="172" ht="14.25" customHeight="1">
@@ -13821,7 +13862,7 @@
         <v>79</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="173" ht="14.25" customHeight="1">
@@ -13841,7 +13882,7 @@
         <v>73</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="174" ht="14.25" customHeight="1">
@@ -13861,7 +13902,7 @@
         <v>89</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="175" ht="14.25" customHeight="1">
@@ -13881,7 +13922,7 @@
         <v>93</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
@@ -13901,7 +13942,7 @@
         <v>99</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
@@ -13921,7 +13962,7 @@
         <v>104</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="178" ht="14.25" customHeight="1">
@@ -13941,7 +13982,7 @@
         <v>59</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="179" ht="14.25" customHeight="1">
@@ -13952,7 +13993,7 @@
         <v>81</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>53</v>
@@ -13961,13 +14002,13 @@
         <v>50</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="180" ht="14.25" customHeight="1">
@@ -13978,7 +14019,7 @@
         <v>81</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>53</v>
@@ -13987,13 +14028,13 @@
         <v>56</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
@@ -14013,7 +14054,7 @@
         <v>50</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
@@ -14033,7 +14074,7 @@
         <v>56</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -14053,7 +14094,7 @@
         <v>61</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
@@ -14073,7 +14114,7 @@
         <v>65</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="185" ht="14.25" customHeight="1">
@@ -14090,7 +14131,7 @@
         <v>50</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="186" ht="14.25" customHeight="1">
@@ -14107,7 +14148,7 @@
         <v>56</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="187" ht="14.25" customHeight="1">
@@ -14124,7 +14165,7 @@
         <v>61</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
@@ -14141,7 +14182,7 @@
         <v>65</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -14149,7 +14190,7 @@
         <v>134</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>53</v>
@@ -14158,7 +14199,7 @@
         <v>50</v>
       </c>
       <c r="F189" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="190" ht="14.25" customHeight="1">
@@ -14166,7 +14207,7 @@
         <v>134</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>53</v>
@@ -14175,7 +14216,7 @@
         <v>56</v>
       </c>
       <c r="F190" s="5" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="191" ht="14.25" customHeight="1">
@@ -14183,16 +14224,16 @@
         <v>134</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="192" ht="14.25" customHeight="1">
@@ -14200,7 +14241,7 @@
         <v>139</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>72</v>
@@ -14212,7 +14253,7 @@
         <v>50</v>
       </c>
       <c r="H192" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="193" ht="14.25" customHeight="1">
@@ -14220,7 +14261,7 @@
         <v>139</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>72</v>
@@ -14232,7 +14273,7 @@
         <v>56</v>
       </c>
       <c r="H193" s="5" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="194" ht="14.25" customHeight="1">
@@ -14240,30 +14281,30 @@
         <v>139</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>72</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="195" ht="14.25" customHeight="1">
       <c r="A195" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>53</v>
@@ -14272,10 +14313,10 @@
         <v>50</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>26</v>
@@ -14283,13 +14324,13 @@
     </row>
     <row r="196" ht="14.25" customHeight="1">
       <c r="A196" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>53</v>
@@ -14301,21 +14342,21 @@
         <v>34</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H196" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="197" ht="14.25" customHeight="1">
       <c r="A197" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>53</v>
@@ -14324,24 +14365,24 @@
         <v>61</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H197" s="2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="198" ht="14.25" customHeight="1">
       <c r="A198" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>53</v>
@@ -14350,10 +14391,10 @@
         <v>65</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>25</v>
@@ -14364,10 +14405,10 @@
         <v>346</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>53</v>
@@ -14376,7 +14417,7 @@
         <v>50</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>25</v>
@@ -14387,7 +14428,7 @@
         <v>112</v>
       </c>
       <c r="B200" s="8" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C200" s="8"/>
       <c r="D200" s="8" t="s">
@@ -14397,10 +14438,10 @@
         <v>50</v>
       </c>
       <c r="F200" s="8" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="G200" s="8" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H200" s="8" t="s">
         <v>25</v>
@@ -14411,7 +14452,7 @@
         <v>112</v>
       </c>
       <c r="B201" s="8" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C201" s="8"/>
       <c r="D201" s="8" t="s">
@@ -14421,10 +14462,10 @@
         <v>56</v>
       </c>
       <c r="F201" s="8" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="G201" s="8" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H201" s="8" t="s">
         <v>26</v>
@@ -14435,7 +14476,7 @@
         <v>416</v>
       </c>
       <c r="B202" s="7" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C202" s="8"/>
       <c r="D202" s="8" t="s">
@@ -14449,7 +14490,7 @@
       </c>
       <c r="G202" s="8"/>
       <c r="H202" s="7" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -14457,7 +14498,7 @@
         <v>416</v>
       </c>
       <c r="B203" s="7" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C203" s="8"/>
       <c r="D203" s="8" t="s">
@@ -14471,7 +14512,7 @@
       </c>
       <c r="G203" s="8"/>
       <c r="H203" s="7" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
@@ -14479,7 +14520,7 @@
         <v>418</v>
       </c>
       <c r="B204" s="7" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C204" s="8"/>
       <c r="D204" s="8" t="s">
@@ -14493,7 +14534,7 @@
       </c>
       <c r="G204" s="8"/>
       <c r="H204" s="7" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="205" ht="14.25" customHeight="1">
@@ -14501,7 +14542,7 @@
         <v>418</v>
       </c>
       <c r="B205" s="7" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C205" s="8"/>
       <c r="D205" s="8" t="s">
@@ -14515,7 +14556,7 @@
       </c>
       <c r="G205" s="8"/>
       <c r="H205" s="7" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="206" ht="14.25" customHeight="1"/>
@@ -15225,61 +15266,61 @@
         <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1"/>
@@ -16312,19 +16353,19 @@
         <v>422</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>46</v>
@@ -16335,13 +16376,13 @@
         <v>394</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D2" s="9" t="s">
         <v>586</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
@@ -16349,13 +16390,13 @@
         <v>234</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>588</v>
+        <v>586</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
@@ -16363,13 +16404,13 @@
         <v>240</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>590</v>
+        <v>586</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>591</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
@@ -16377,13 +16418,13 @@
         <v>248</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>592</v>
+        <v>586</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
@@ -16391,13 +16432,13 @@
         <v>237</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>594</v>
+        <v>586</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>595</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
@@ -16405,13 +16446,13 @@
         <v>244</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>596</v>
+        <v>586</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
@@ -16419,13 +16460,13 @@
         <v>222</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>598</v>
+        <v>586</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
@@ -16433,13 +16474,13 @@
         <v>230</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>600</v>
+        <v>586</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
@@ -16447,13 +16488,13 @@
         <v>226</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>602</v>
+        <v>586</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>603</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
@@ -16461,13 +16502,13 @@
         <v>407</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>604</v>
+        <v>586</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
@@ -16475,13 +16516,13 @@
         <v>409</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>606</v>
+        <v>586</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>607</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
@@ -16489,13 +16530,13 @@
         <v>411</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>608</v>
+        <v>586</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>609</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
@@ -16503,13 +16544,13 @@
         <v>413</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>610</v>
+        <v>586</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>611</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
@@ -16517,13 +16558,13 @@
         <v>189</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>612</v>
+        <v>586</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>613</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
@@ -16531,13 +16572,13 @@
         <v>388</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>614</v>
+        <v>586</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
@@ -16545,13 +16586,13 @@
         <v>391</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>616</v>
+        <v>586</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>617</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
@@ -16559,13 +16600,13 @@
         <v>397</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>618</v>
+        <v>586</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
@@ -16573,13 +16614,13 @@
         <v>253</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>620</v>
+        <v>586</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
@@ -16587,13 +16628,13 @@
         <v>400</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>622</v>
+        <v>586</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>623</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
@@ -16604,10 +16645,10 @@
         <v>74</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>623</v>
+        <v>586</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>624</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
@@ -16615,13 +16656,13 @@
         <v>292</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>625</v>
+        <v>586</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>626</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
@@ -16629,13 +16670,13 @@
         <v>299</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>627</v>
+        <v>586</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>628</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
@@ -16646,10 +16687,10 @@
         <v>98</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>628</v>
+        <v>586</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1">
@@ -16660,10 +16701,10 @@
         <v>367</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>629</v>
+        <v>586</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>630</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
@@ -16671,13 +16712,13 @@
         <v>354</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>631</v>
+        <v>586</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>632</v>
       </c>
     </row>
     <row r="27" ht="14.25" customHeight="1">
@@ -16685,13 +16726,13 @@
         <v>357</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>633</v>
+        <v>586</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>634</v>
       </c>
     </row>
     <row r="28" ht="14.25" customHeight="1">
@@ -16702,10 +16743,10 @@
         <v>343</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>634</v>
+        <v>586</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>635</v>
       </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
@@ -16716,10 +16757,10 @@
         <v>314</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>635</v>
+        <v>586</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>636</v>
       </c>
     </row>
     <row r="30" ht="14.25" customHeight="1">
@@ -16730,10 +16771,10 @@
         <v>121</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>636</v>
+        <v>586</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>637</v>
       </c>
     </row>
     <row r="31" ht="14.25" customHeight="1">
@@ -16744,10 +16785,10 @@
         <v>360</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>637</v>
+        <v>586</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>638</v>
       </c>
     </row>
     <row r="32" ht="14.25" customHeight="1">
@@ -16758,10 +16799,10 @@
         <v>175</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>638</v>
+        <v>586</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>639</v>
       </c>
     </row>
     <row r="33" ht="14.25" customHeight="1">
@@ -16772,10 +16813,10 @@
         <v>309</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>639</v>
+        <v>586</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>640</v>
       </c>
     </row>
     <row r="34" ht="14.25" customHeight="1">
@@ -16786,10 +16827,10 @@
         <v>321</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>640</v>
+        <v>586</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>641</v>
       </c>
     </row>
     <row r="35" ht="14.25" customHeight="1">
@@ -16800,10 +16841,10 @@
         <v>129</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>641</v>
+        <v>586</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>642</v>
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1">
@@ -16814,10 +16855,10 @@
         <v>318</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>642</v>
+        <v>586</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>643</v>
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1">
@@ -16828,10 +16869,10 @@
         <v>117</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>643</v>
+        <v>586</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>644</v>
       </c>
     </row>
     <row r="38" ht="14.25" customHeight="1">
@@ -16839,13 +16880,13 @@
         <v>380</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>645</v>
+        <v>586</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>646</v>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
@@ -16853,13 +16894,13 @@
         <v>372</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>647</v>
+        <v>586</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>648</v>
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1">
@@ -16870,10 +16911,10 @@
         <v>144</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>648</v>
+        <v>586</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>649</v>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1">
@@ -16884,10 +16925,10 @@
         <v>135</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>649</v>
+        <v>586</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>650</v>
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1">
@@ -16898,10 +16939,10 @@
         <v>167</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>650</v>
+        <v>586</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>651</v>
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1">
@@ -16912,10 +16953,10 @@
         <v>171</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>651</v>
+        <v>586</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>652</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
@@ -16926,10 +16967,10 @@
         <v>153</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>652</v>
+        <v>586</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="45" ht="14.25" customHeight="1">
@@ -16940,10 +16981,10 @@
         <v>163</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>653</v>
+        <v>586</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>654</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1">
@@ -16954,10 +16995,10 @@
         <v>158</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>654</v>
+        <v>586</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
@@ -16968,10 +17009,10 @@
         <v>363</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>655</v>
+        <v>586</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>656</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1"/>
@@ -17912,10 +17953,10 @@
         <v>421</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>46</v>
@@ -17926,7 +17967,7 @@
         <v>402</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
@@ -17934,7 +17975,7 @@
         <v>182</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
@@ -17942,23 +17983,23 @@
         <v>258</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1"/>
@@ -18982,21 +19023,21 @@
         <v>421</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1"/>
